--- a/research/traditional_assets/database/data/taiwan/taiwan_diversified.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_diversified.xlsx
@@ -1151,7 +1151,7 @@
         <v>5159.4</v>
       </c>
       <c r="L2">
-        <v>9629.817321921581</v>
+        <v>9629.81732192157</v>
       </c>
       <c r="M2">
         <v>12788.7</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08315957847594085</v>
+        <v>0.08302925931898897</v>
       </c>
       <c r="C2">
-        <v>12235.44249806821</v>
+        <v>12137.40436892537</v>
       </c>
       <c r="D2">
-        <v>11273.94249806821</v>
+        <v>11313.40636892537</v>
       </c>
       <c r="E2">
-        <v>-8590.799999999999</v>
+        <v>-8453.297999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>137.502</v>
       </c>
       <c r="G2">
         <v>961.5</v>
@@ -1451,28 +1451,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.916350599999999</v>
       </c>
       <c r="N2">
-        <v>566.9326530612244</v>
+        <v>560.0163024612244</v>
       </c>
       <c r="O2">
-        <v>113.3865306122449</v>
+        <v>112.0032604922449</v>
       </c>
       <c r="P2">
-        <v>453.5461224489795</v>
+        <v>448.0130419689796</v>
       </c>
       <c r="Q2">
-        <v>1213.246122448979</v>
+        <v>1207.713041968979</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08315957847594085</v>
+        <v>0.08346147405958482</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7340922286861121</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>81.96991243636847</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08302925931898897</v>
+        <v>0.08289894016203708</v>
       </c>
       <c r="C3">
-        <v>12137.40436892537</v>
+        <v>12039.64349289853</v>
       </c>
       <c r="D3">
-        <v>11313.40636892537</v>
+        <v>11353.14749289853</v>
       </c>
       <c r="E3">
-        <v>-8453.297999999999</v>
+        <v>-8315.795999999998</v>
       </c>
       <c r="F3">
-        <v>137.502</v>
+        <v>275.004</v>
       </c>
       <c r="G3">
         <v>961.5</v>
@@ -1533,28 +1533,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M3">
-        <v>6.916350599999999</v>
+        <v>13.8327012</v>
       </c>
       <c r="N3">
-        <v>560.0163024612244</v>
+        <v>553.0999518612244</v>
       </c>
       <c r="O3">
-        <v>112.0032604922449</v>
+        <v>110.6199903722449</v>
       </c>
       <c r="P3">
-        <v>448.0130419689796</v>
+        <v>442.4799614889795</v>
       </c>
       <c r="Q3">
-        <v>1207.713041968979</v>
+        <v>1202.179961488979</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08346147405958482</v>
+        <v>0.08376953077758886</v>
       </c>
       <c r="T3">
-        <v>0.7340922286861121</v>
+        <v>0.7400968275056786</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>81.96991243636847</v>
+        <v>40.98495621818424</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08289894016203708</v>
+        <v>0.08276862100508521</v>
       </c>
       <c r="C4">
-        <v>12039.64349289853</v>
+        <v>11942.16280204667</v>
       </c>
       <c r="D4">
-        <v>11353.14749289853</v>
+        <v>11393.16880204667</v>
       </c>
       <c r="E4">
-        <v>-8315.795999999998</v>
+        <v>-8178.293999999999</v>
       </c>
       <c r="F4">
-        <v>275.004</v>
+        <v>412.506</v>
       </c>
       <c r="G4">
         <v>961.5</v>
@@ -1615,28 +1615,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M4">
-        <v>13.8327012</v>
+        <v>20.7490518</v>
       </c>
       <c r="N4">
-        <v>553.0999518612244</v>
+        <v>546.1836012612245</v>
       </c>
       <c r="O4">
-        <v>110.6199903722449</v>
+        <v>109.2367202522449</v>
       </c>
       <c r="P4">
-        <v>442.4799614889795</v>
+        <v>436.9468810089796</v>
       </c>
       <c r="Q4">
-        <v>1202.179961488979</v>
+        <v>1196.64688100898</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08376953077758886</v>
+        <v>0.08408393918050021</v>
       </c>
       <c r="T4">
-        <v>0.7400968275056786</v>
+        <v>0.7462252324864733</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>40.98495621818424</v>
+        <v>27.32330414545616</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08276862100508521</v>
+        <v>0.08263830184813332</v>
       </c>
       <c r="C5">
-        <v>11942.16280204667</v>
+        <v>11844.96526991856</v>
       </c>
       <c r="D5">
-        <v>11393.16880204667</v>
+        <v>11433.47326991856</v>
       </c>
       <c r="E5">
-        <v>-8178.293999999999</v>
+        <v>-8040.791999999999</v>
       </c>
       <c r="F5">
-        <v>412.506</v>
+        <v>550.0079999999999</v>
       </c>
       <c r="G5">
         <v>961.5</v>
@@ -1697,28 +1697,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M5">
-        <v>20.7490518</v>
+        <v>27.66540239999999</v>
       </c>
       <c r="N5">
-        <v>546.1836012612245</v>
+        <v>539.2672506612245</v>
       </c>
       <c r="O5">
-        <v>109.2367202522449</v>
+        <v>107.8534501322449</v>
       </c>
       <c r="P5">
-        <v>436.9468810089796</v>
+        <v>431.4138005289796</v>
       </c>
       <c r="Q5">
-        <v>1196.64688100898</v>
+        <v>1191.113800528979</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08408393918050021</v>
+        <v>0.08440489775847221</v>
       </c>
       <c r="T5">
-        <v>0.7462252324864733</v>
+        <v>0.7524813125710348</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.32330414545616</v>
+        <v>20.49247810909212</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08263830184813332</v>
+        <v>0.08250798269118144</v>
       </c>
       <c r="C6">
-        <v>11844.96526991856</v>
+        <v>11748.05391228926</v>
       </c>
       <c r="D6">
-        <v>11433.47326991856</v>
+        <v>11474.06391228926</v>
       </c>
       <c r="E6">
-        <v>-8040.791999999999</v>
+        <v>-7903.289999999999</v>
       </c>
       <c r="F6">
-        <v>550.0079999999999</v>
+        <v>687.51</v>
       </c>
       <c r="G6">
         <v>961.5</v>
@@ -1779,28 +1779,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M6">
-        <v>27.66540239999999</v>
+        <v>34.581753</v>
       </c>
       <c r="N6">
-        <v>539.2672506612245</v>
+        <v>532.3509000612244</v>
       </c>
       <c r="O6">
-        <v>107.8534501322449</v>
+        <v>106.4701800122449</v>
       </c>
       <c r="P6">
-        <v>431.4138005289796</v>
+        <v>425.8807200489795</v>
       </c>
       <c r="Q6">
-        <v>1191.113800528979</v>
+        <v>1185.580720048979</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08440489775847221</v>
+        <v>0.08473261335913836</v>
       </c>
       <c r="T6">
-        <v>0.7524813125710348</v>
+        <v>0.7588690996047446</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.49247810909212</v>
+        <v>16.39398248727369</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08250798269118144</v>
+        <v>0.08237766353422957</v>
       </c>
       <c r="C7">
-        <v>11748.05391228926</v>
+        <v>11651.43178791232</v>
       </c>
       <c r="D7">
-        <v>11474.06391228926</v>
+        <v>11514.94378791233</v>
       </c>
       <c r="E7">
-        <v>-7903.289999999999</v>
+        <v>-7765.788</v>
       </c>
       <c r="F7">
-        <v>687.51</v>
+        <v>825.0119999999999</v>
       </c>
       <c r="G7">
         <v>961.5</v>
@@ -1861,28 +1861,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M7">
-        <v>34.581753</v>
+        <v>41.49810359999999</v>
       </c>
       <c r="N7">
-        <v>532.3509000612244</v>
+        <v>525.4345494612244</v>
       </c>
       <c r="O7">
-        <v>106.4701800122449</v>
+        <v>105.0869098922449</v>
       </c>
       <c r="P7">
-        <v>425.8807200489795</v>
+        <v>420.3476395689795</v>
       </c>
       <c r="Q7">
-        <v>1185.580720048979</v>
+        <v>1180.047639568979</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08473261335913836</v>
+        <v>0.08506730163215911</v>
       </c>
       <c r="T7">
-        <v>0.7588690996047446</v>
+        <v>0.765392797000874</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.39398248727369</v>
+        <v>13.66165207272808</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08237766353422957</v>
+        <v>0.08224734437727768</v>
       </c>
       <c r="C8">
-        <v>11651.43178791232</v>
+        <v>11555.10199928816</v>
       </c>
       <c r="D8">
-        <v>11514.94378791233</v>
+        <v>11556.11599928816</v>
       </c>
       <c r="E8">
-        <v>-7765.788</v>
+        <v>-7628.285999999999</v>
       </c>
       <c r="F8">
-        <v>825.0119999999999</v>
+        <v>962.5139999999998</v>
       </c>
       <c r="G8">
         <v>961.5</v>
@@ -1943,28 +1943,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M8">
-        <v>41.49810359999999</v>
+        <v>48.41445419999999</v>
       </c>
       <c r="N8">
-        <v>525.4345494612244</v>
+        <v>518.5181988612244</v>
       </c>
       <c r="O8">
-        <v>105.0869098922449</v>
+        <v>103.7036397722449</v>
       </c>
       <c r="P8">
-        <v>420.3476395689795</v>
+        <v>414.8145590889795</v>
       </c>
       <c r="Q8">
-        <v>1180.047639568979</v>
+        <v>1174.514559088979</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08506730163215911</v>
+        <v>0.08540918750244912</v>
       </c>
       <c r="T8">
-        <v>0.765392797000874</v>
+        <v>0.7720567889646621</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>13.66165207272808</v>
+        <v>11.70998749090978</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08224734437727767</v>
+        <v>0.08211702522032582</v>
       </c>
       <c r="C9">
-        <v>11555.10199928816</v>
+        <v>11459.06769344892</v>
       </c>
       <c r="D9">
-        <v>11556.11599928816</v>
+        <v>11597.58369344892</v>
       </c>
       <c r="E9">
-        <v>-7628.285999999999</v>
+        <v>-7490.784</v>
       </c>
       <c r="F9">
-        <v>962.514</v>
+        <v>1100.016</v>
       </c>
       <c r="G9">
         <v>961.5</v>
@@ -2025,28 +2025,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M9">
-        <v>48.4144542</v>
+        <v>55.33080479999999</v>
       </c>
       <c r="N9">
-        <v>518.5181988612244</v>
+        <v>511.6018482612244</v>
       </c>
       <c r="O9">
-        <v>103.7036397722449</v>
+        <v>102.3203696522449</v>
       </c>
       <c r="P9">
-        <v>414.8145590889795</v>
+        <v>409.2814786089795</v>
       </c>
       <c r="Q9">
-        <v>1174.514559088979</v>
+        <v>1168.981478608979</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08540918750244912</v>
+        <v>0.08575850567426718</v>
       </c>
       <c r="T9">
-        <v>0.7720567889646621</v>
+        <v>0.7788656503189673</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.70998749090978</v>
+        <v>10.24623905454606</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08211702522032582</v>
+        <v>0.08198670606337392</v>
       </c>
       <c r="C10">
-        <v>11459.06769344892</v>
+        <v>11363.33206276042</v>
       </c>
       <c r="D10">
-        <v>11597.58369344892</v>
+        <v>11639.35006276042</v>
       </c>
       <c r="E10">
-        <v>-7490.784</v>
+        <v>-7353.281999999999</v>
       </c>
       <c r="F10">
-        <v>1100.016</v>
+        <v>1237.518</v>
       </c>
       <c r="G10">
         <v>961.5</v>
@@ -2107,28 +2107,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M10">
-        <v>55.33080479999999</v>
+        <v>62.24715539999999</v>
       </c>
       <c r="N10">
-        <v>511.6018482612244</v>
+        <v>504.6854976612244</v>
       </c>
       <c r="O10">
-        <v>102.3203696522449</v>
+        <v>100.9370995322449</v>
       </c>
       <c r="P10">
-        <v>409.2814786089795</v>
+        <v>403.7483981289795</v>
       </c>
       <c r="Q10">
-        <v>1168.981478608979</v>
+        <v>1163.44839812898</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08575850567426718</v>
+        <v>0.08611550116854276</v>
       </c>
       <c r="T10">
-        <v>0.7788656503189673</v>
+        <v>0.7858241569777625</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.24623905454606</v>
+        <v>9.107768048485385</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08198670606337392</v>
+        <v>0.08197638690642202</v>
       </c>
       <c r="C11">
-        <v>11363.33206276042</v>
+        <v>11229.15013671989</v>
       </c>
       <c r="D11">
-        <v>11639.35006276042</v>
+        <v>11642.67013671989</v>
       </c>
       <c r="E11">
-        <v>-7353.281999999999</v>
+        <v>-7215.78</v>
       </c>
       <c r="F11">
-        <v>1237.518</v>
+        <v>1375.02</v>
       </c>
       <c r="G11">
         <v>961.5</v>
@@ -2189,45 +2189,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M11">
-        <v>62.24715539999999</v>
+        <v>71.22603599999998</v>
       </c>
       <c r="N11">
-        <v>504.6854976612244</v>
+        <v>495.7066170612244</v>
       </c>
       <c r="O11">
-        <v>100.9370995322449</v>
+        <v>99.1413234122449</v>
       </c>
       <c r="P11">
-        <v>403.7483981289795</v>
+        <v>396.5652936489795</v>
       </c>
       <c r="Q11">
-        <v>1163.44839812898</v>
+        <v>1156.265293648979</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08611550116854276</v>
+        <v>0.08648042989602447</v>
       </c>
       <c r="T11">
-        <v>0.7858241569777625</v>
+        <v>0.7929372971178644</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.107768048485385</v>
+        <v>7.959626632334623</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08197638690642203</v>
+        <v>0.08185806774947016</v>
       </c>
       <c r="C12">
-        <v>11229.15013671988</v>
+        <v>11129.85181764967</v>
       </c>
       <c r="D12">
-        <v>11642.67013671988</v>
+        <v>11680.87381764967</v>
       </c>
       <c r="E12">
-        <v>-7215.779999999999</v>
+        <v>-7078.277999999999</v>
       </c>
       <c r="F12">
-        <v>1375.02</v>
+        <v>1512.522</v>
       </c>
       <c r="G12">
         <v>961.5</v>
@@ -2271,28 +2271,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M12">
-        <v>71.22603599999999</v>
+        <v>78.3486396</v>
       </c>
       <c r="N12">
-        <v>495.7066170612244</v>
+        <v>488.5840134612244</v>
       </c>
       <c r="O12">
-        <v>99.14132341224489</v>
+        <v>97.71680269224488</v>
       </c>
       <c r="P12">
-        <v>396.5652936489795</v>
+        <v>390.8672107689795</v>
       </c>
       <c r="Q12">
-        <v>1156.265293648979</v>
+        <v>1150.56721076898</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08648042989602449</v>
+        <v>0.08685355926906758</v>
       </c>
       <c r="T12">
-        <v>0.7929372971178646</v>
+        <v>0.8002102831038114</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.95962663233462</v>
+        <v>7.236024211213291</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08185806774947016</v>
+        <v>0.08190294859251827</v>
       </c>
       <c r="C13">
-        <v>11129.85181764967</v>
+        <v>10977.82891326616</v>
       </c>
       <c r="D13">
-        <v>11680.87381764967</v>
+        <v>11666.35291326616</v>
       </c>
       <c r="E13">
-        <v>-7078.277999999999</v>
+        <v>-6940.776</v>
       </c>
       <c r="F13">
-        <v>1512.522</v>
+        <v>1650.024</v>
       </c>
       <c r="G13">
         <v>961.5</v>
@@ -2353,45 +2353,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M13">
-        <v>78.3486396</v>
+        <v>88.27628399999999</v>
       </c>
       <c r="N13">
-        <v>488.5840134612244</v>
+        <v>478.6563690612244</v>
       </c>
       <c r="O13">
-        <v>97.71680269224488</v>
+        <v>95.73127381224489</v>
       </c>
       <c r="P13">
-        <v>390.8672107689795</v>
+        <v>382.9250952489796</v>
       </c>
       <c r="Q13">
-        <v>1150.56721076898</v>
+        <v>1142.62509524898</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08685355926906758</v>
+        <v>0.0872351688551344</v>
       </c>
       <c r="T13">
-        <v>0.8002102831038114</v>
+        <v>0.8076485642258027</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.236024211213291</v>
+        <v>6.422253264095535</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08190294859251827</v>
+        <v>0.08179822943556637</v>
       </c>
       <c r="C14">
-        <v>10977.82891326616</v>
+        <v>10874.26443355358</v>
       </c>
       <c r="D14">
-        <v>11666.35291326616</v>
+        <v>11700.29043355357</v>
       </c>
       <c r="E14">
-        <v>-6940.776</v>
+        <v>-6803.273999999999</v>
       </c>
       <c r="F14">
-        <v>1650.024</v>
+        <v>1787.526</v>
       </c>
       <c r="G14">
         <v>961.5</v>
@@ -2435,28 +2435,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M14">
-        <v>88.27628399999999</v>
+        <v>95.63264099999999</v>
       </c>
       <c r="N14">
-        <v>478.6563690612244</v>
+        <v>471.3000120612244</v>
       </c>
       <c r="O14">
-        <v>95.73127381224489</v>
+        <v>94.26000241224489</v>
       </c>
       <c r="P14">
-        <v>382.9250952489796</v>
+        <v>377.0400096489795</v>
       </c>
       <c r="Q14">
-        <v>1142.62509524898</v>
+        <v>1136.74000964898</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0872351688551344</v>
+        <v>0.08762555107536366</v>
       </c>
       <c r="T14">
-        <v>0.8076485642258027</v>
+        <v>0.8152578403161154</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.422253264095535</v>
+        <v>5.928233782242033</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08179822943556637</v>
+        <v>0.08178311027861451</v>
       </c>
       <c r="C15">
-        <v>10874.26443355358</v>
+        <v>10741.67858799596</v>
       </c>
       <c r="D15">
-        <v>11700.29043355357</v>
+        <v>11705.20658799596</v>
       </c>
       <c r="E15">
-        <v>-6803.273999999999</v>
+        <v>-6665.771999999999</v>
       </c>
       <c r="F15">
-        <v>1787.526</v>
+        <v>1925.028</v>
       </c>
       <c r="G15">
         <v>961.5</v>
@@ -2517,45 +2517,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M15">
-        <v>95.63264099999999</v>
+        <v>104.5290204</v>
       </c>
       <c r="N15">
-        <v>471.3000120612244</v>
+        <v>462.4036326612244</v>
       </c>
       <c r="O15">
-        <v>94.26000241224489</v>
+        <v>92.48072653224489</v>
       </c>
       <c r="P15">
-        <v>377.0400096489795</v>
+        <v>369.9229061289795</v>
       </c>
       <c r="Q15">
-        <v>1136.74000964898</v>
+        <v>1129.622906128979</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08762555107536366</v>
+        <v>0.08802501195187734</v>
       </c>
       <c r="T15">
-        <v>0.8152578403161154</v>
+        <v>0.8230440763155054</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>5.928233782242033</v>
+        <v>5.423686655550293</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08178311027861451</v>
+        <v>0.08168479112166263</v>
       </c>
       <c r="C16">
-        <v>10741.67858799596</v>
+        <v>10636.24716741713</v>
       </c>
       <c r="D16">
-        <v>11705.20658799596</v>
+        <v>11737.27716741713</v>
       </c>
       <c r="E16">
-        <v>-6665.771999999999</v>
+        <v>-6528.269999999999</v>
       </c>
       <c r="F16">
-        <v>1925.028</v>
+        <v>2062.53</v>
       </c>
       <c r="G16">
         <v>961.5</v>
@@ -2599,28 +2599,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M16">
-        <v>104.5290204</v>
+        <v>111.995379</v>
       </c>
       <c r="N16">
-        <v>462.4036326612244</v>
+        <v>454.9372740612244</v>
       </c>
       <c r="O16">
-        <v>92.48072653224489</v>
+        <v>90.98745481224489</v>
       </c>
       <c r="P16">
-        <v>369.9229061289795</v>
+        <v>363.9498192489795</v>
       </c>
       <c r="Q16">
-        <v>1129.622906128979</v>
+        <v>1123.649819248979</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08802501195187734</v>
+        <v>0.08843387190783839</v>
       </c>
       <c r="T16">
-        <v>0.8230440763155054</v>
+        <v>0.831013517867822</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.423686655550293</v>
+        <v>5.062107545180274</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08168479112166263</v>
+        <v>0.08158647196471072</v>
       </c>
       <c r="C17">
-        <v>10636.24716741714</v>
+        <v>10530.99196718967</v>
       </c>
       <c r="D17">
-        <v>11737.27716741713</v>
+        <v>11769.52396718967</v>
       </c>
       <c r="E17">
-        <v>-6528.27</v>
+        <v>-6390.768</v>
       </c>
       <c r="F17">
-        <v>2062.53</v>
+        <v>2200.032</v>
       </c>
       <c r="G17">
         <v>961.5</v>
@@ -2681,28 +2681,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M17">
-        <v>111.995379</v>
+        <v>119.4617376</v>
       </c>
       <c r="N17">
-        <v>454.9372740612245</v>
+        <v>447.4709154612244</v>
       </c>
       <c r="O17">
-        <v>90.98745481224489</v>
+        <v>89.4941830922449</v>
       </c>
       <c r="P17">
-        <v>363.9498192489796</v>
+        <v>357.9767323689795</v>
       </c>
       <c r="Q17">
-        <v>1123.649819248979</v>
+        <v>1117.676732368979</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08843387190783839</v>
+        <v>0.08885246662465564</v>
       </c>
       <c r="T17">
-        <v>0.831013517867822</v>
+        <v>0.8391727080285271</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.062107545180275</v>
+        <v>4.745725823606508</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08158647196471072</v>
+        <v>0.08148815280775884</v>
       </c>
       <c r="C18">
-        <v>10530.99196718967</v>
+        <v>10425.9144437495</v>
       </c>
       <c r="D18">
-        <v>11769.52396718967</v>
+        <v>11801.9484437495</v>
       </c>
       <c r="E18">
-        <v>-6390.768</v>
+        <v>-6253.266</v>
       </c>
       <c r="F18">
-        <v>2200.032</v>
+        <v>2337.534</v>
       </c>
       <c r="G18">
         <v>961.5</v>
@@ -2763,28 +2763,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M18">
-        <v>119.4617376</v>
+        <v>126.9280962</v>
       </c>
       <c r="N18">
-        <v>447.4709154612244</v>
+        <v>440.0045568612244</v>
       </c>
       <c r="O18">
-        <v>89.4941830922449</v>
+        <v>88.00091137224489</v>
       </c>
       <c r="P18">
-        <v>357.9767323689795</v>
+        <v>352.0036454889795</v>
       </c>
       <c r="Q18">
-        <v>1117.676732368979</v>
+        <v>1111.703645488979</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08885246662465564</v>
+        <v>0.08928114796115524</v>
       </c>
       <c r="T18">
-        <v>0.8391727080285271</v>
+        <v>0.8475285051810565</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.745725823606508</v>
+        <v>4.466565481041417</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08148815280775884</v>
+        <v>0.08153383365080699</v>
       </c>
       <c r="C19">
-        <v>10425.9144437495</v>
+        <v>10273.32525887621</v>
       </c>
       <c r="D19">
-        <v>11801.9484437495</v>
+        <v>11786.86125887621</v>
       </c>
       <c r="E19">
-        <v>-6253.266</v>
+        <v>-6115.763999999999</v>
       </c>
       <c r="F19">
-        <v>2337.534</v>
+        <v>2475.036</v>
       </c>
       <c r="G19">
         <v>961.5</v>
@@ -2845,45 +2845,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M19">
-        <v>126.9280962</v>
+        <v>136.8694908</v>
       </c>
       <c r="N19">
-        <v>440.0045568612244</v>
+        <v>430.0631622612244</v>
       </c>
       <c r="O19">
-        <v>88.00091137224489</v>
+        <v>86.01263245224489</v>
       </c>
       <c r="P19">
-        <v>352.0036454889795</v>
+        <v>344.0505298089795</v>
       </c>
       <c r="Q19">
-        <v>1111.703645488979</v>
+        <v>1103.75052980898</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08928114796115524</v>
+        <v>0.08972028494000853</v>
       </c>
       <c r="T19">
-        <v>0.8475285051810565</v>
+        <v>0.8560881022641356</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.466565481041417</v>
+        <v>4.142140441580604</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08153383365080699</v>
+        <v>0.0814435144938551</v>
       </c>
       <c r="C20">
-        <v>10273.32525887621</v>
+        <v>10165.69066637313</v>
       </c>
       <c r="D20">
-        <v>11786.86125887621</v>
+        <v>11816.72866637313</v>
       </c>
       <c r="E20">
-        <v>-6115.763999999999</v>
+        <v>-5978.261999999999</v>
       </c>
       <c r="F20">
-        <v>2475.036</v>
+        <v>2612.538</v>
       </c>
       <c r="G20">
         <v>961.5</v>
@@ -2927,28 +2927,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M20">
-        <v>136.8694908</v>
+        <v>144.4733514</v>
       </c>
       <c r="N20">
-        <v>430.0631622612244</v>
+        <v>422.4593016612244</v>
       </c>
       <c r="O20">
-        <v>86.01263245224489</v>
+        <v>84.49186033224488</v>
       </c>
       <c r="P20">
-        <v>344.0505298089795</v>
+        <v>337.9674413289795</v>
       </c>
       <c r="Q20">
-        <v>1103.75052980898</v>
+        <v>1097.66744132898</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08972028494000851</v>
+        <v>0.09017026480722852</v>
       </c>
       <c r="T20">
-        <v>0.8560881022641355</v>
+        <v>0.8648590474233399</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.142140441580604</v>
+        <v>3.924133049918467</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0814435144938551</v>
+        <v>0.08135319533690322</v>
       </c>
       <c r="C21">
-        <v>10165.69066637313</v>
+        <v>10058.20782389083</v>
       </c>
       <c r="D21">
-        <v>11816.72866637313</v>
+        <v>11846.74782389083</v>
       </c>
       <c r="E21">
-        <v>-5978.261999999999</v>
+        <v>-5840.759999999999</v>
       </c>
       <c r="F21">
-        <v>2612.538</v>
+        <v>2750.04</v>
       </c>
       <c r="G21">
         <v>961.5</v>
@@ -3009,28 +3009,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M21">
-        <v>144.4733514</v>
+        <v>152.077212</v>
       </c>
       <c r="N21">
-        <v>422.4593016612244</v>
+        <v>414.8554410612244</v>
       </c>
       <c r="O21">
-        <v>84.49186033224488</v>
+        <v>82.97108821224488</v>
       </c>
       <c r="P21">
-        <v>337.9674413289795</v>
+        <v>331.8843528489795</v>
       </c>
       <c r="Q21">
-        <v>1097.66744132898</v>
+        <v>1091.58435284898</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09017026480722852</v>
+        <v>0.09063149417112902</v>
       </c>
       <c r="T21">
-        <v>0.8648590474233399</v>
+        <v>0.8738492662115241</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.924133049918467</v>
+        <v>3.727926397422543</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08135319533690322</v>
+        <v>0.08126287617995134</v>
       </c>
       <c r="C22">
-        <v>10058.20782389083</v>
+        <v>9950.877890889737</v>
       </c>
       <c r="D22">
-        <v>11846.74782389083</v>
+        <v>11876.91989088974</v>
       </c>
       <c r="E22">
-        <v>-5840.759999999999</v>
+        <v>-5703.258</v>
       </c>
       <c r="F22">
-        <v>2750.04</v>
+        <v>2887.542</v>
       </c>
       <c r="G22">
         <v>961.5</v>
@@ -3091,28 +3091,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M22">
-        <v>152.077212</v>
+        <v>159.6810726</v>
       </c>
       <c r="N22">
-        <v>414.8554410612244</v>
+        <v>407.2515804612244</v>
       </c>
       <c r="O22">
-        <v>82.97108821224488</v>
+        <v>81.45031609224489</v>
       </c>
       <c r="P22">
-        <v>331.8843528489795</v>
+        <v>325.8012643689796</v>
       </c>
       <c r="Q22">
-        <v>1091.58435284898</v>
+        <v>1085.501264368979</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09063149417112902</v>
+        <v>0.0911044002277865</v>
       </c>
       <c r="T22">
-        <v>0.8738492662115241</v>
+        <v>0.8830670854753588</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.727926397422543</v>
+        <v>3.550406092783375</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08126287617995134</v>
+        <v>0.08117255702299946</v>
       </c>
       <c r="C23">
-        <v>9950.877890889737</v>
+        <v>9843.702038672403</v>
       </c>
       <c r="D23">
-        <v>11876.91989088974</v>
+        <v>11907.2460386724</v>
       </c>
       <c r="E23">
-        <v>-5703.258</v>
+        <v>-5565.755999999999</v>
       </c>
       <c r="F23">
-        <v>2887.541999999999</v>
+        <v>3025.044</v>
       </c>
       <c r="G23">
         <v>961.5</v>
@@ -3173,28 +3173,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M23">
-        <v>159.6810726</v>
+        <v>167.2849332</v>
       </c>
       <c r="N23">
-        <v>407.2515804612244</v>
+        <v>399.6477198612244</v>
       </c>
       <c r="O23">
-        <v>81.45031609224489</v>
+        <v>79.92954397224489</v>
       </c>
       <c r="P23">
-        <v>325.8012643689796</v>
+        <v>319.7181758889795</v>
       </c>
       <c r="Q23">
-        <v>1085.501264368979</v>
+        <v>1079.418175888979</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0911044002277865</v>
+        <v>0.09158943208076853</v>
       </c>
       <c r="T23">
-        <v>0.8830670854753588</v>
+        <v>0.8925212590792918</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.550406092783375</v>
+        <v>3.389023997656857</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08117255702299946</v>
+        <v>0.08108223786604755</v>
       </c>
       <c r="C24">
-        <v>9843.702038672403</v>
+        <v>9736.681450535074</v>
       </c>
       <c r="D24">
-        <v>11907.2460386724</v>
+        <v>11937.72745053507</v>
       </c>
       <c r="E24">
-        <v>-5565.755999999999</v>
+        <v>-5428.253999999999</v>
       </c>
       <c r="F24">
-        <v>3025.044</v>
+        <v>3162.546</v>
       </c>
       <c r="G24">
         <v>961.5</v>
@@ -3255,28 +3255,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M24">
-        <v>167.2849332</v>
+        <v>174.8887938</v>
       </c>
       <c r="N24">
-        <v>399.6477198612244</v>
+        <v>392.0438592612244</v>
       </c>
       <c r="O24">
-        <v>79.92954397224489</v>
+        <v>78.40877185224488</v>
       </c>
       <c r="P24">
-        <v>319.7181758889795</v>
+        <v>313.6350874089795</v>
       </c>
       <c r="Q24">
-        <v>1079.418175888979</v>
+        <v>1073.335087408979</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09158943208076853</v>
+        <v>0.09208706216369814</v>
       </c>
       <c r="T24">
-        <v>0.8925212590792918</v>
+        <v>0.9022209956339763</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.389023997656857</v>
+        <v>3.241675128193516</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08108223786604755</v>
+        <v>0.08099191870909571</v>
       </c>
       <c r="C25">
-        <v>9736.681450535074</v>
+        <v>9629.817321921568</v>
       </c>
       <c r="D25">
-        <v>11937.72745053507</v>
+        <v>11968.36532192157</v>
       </c>
       <c r="E25">
-        <v>-5428.253999999999</v>
+        <v>-5290.751999999999</v>
       </c>
       <c r="F25">
-        <v>3162.546</v>
+        <v>3300.048</v>
       </c>
       <c r="G25">
         <v>961.5</v>
@@ -3337,28 +3337,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M25">
-        <v>174.8887938</v>
+        <v>182.4926544</v>
       </c>
       <c r="N25">
-        <v>392.0438592612244</v>
+        <v>384.4399986612244</v>
       </c>
       <c r="O25">
-        <v>78.40877185224488</v>
+        <v>76.88799973224489</v>
       </c>
       <c r="P25">
-        <v>313.6350874089795</v>
+        <v>307.5519989289795</v>
       </c>
       <c r="Q25">
-        <v>1073.335087408979</v>
+        <v>1067.251998928979</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09208706216369814</v>
+        <v>0.09259778777512592</v>
       </c>
       <c r="T25">
-        <v>0.9022209956339763</v>
+        <v>0.9121759884137841</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.241675128193516</v>
+        <v>3.106605331185453</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08099191870909568</v>
+        <v>0.08140159955214381</v>
       </c>
       <c r="C26">
-        <v>9629.817321921579</v>
+        <v>9354.590892214106</v>
       </c>
       <c r="D26">
-        <v>11968.36532192158</v>
+        <v>11830.64089221411</v>
       </c>
       <c r="E26">
-        <v>-5290.751999999999</v>
+        <v>-5153.25</v>
       </c>
       <c r="F26">
-        <v>3300.048</v>
+        <v>3437.55</v>
       </c>
       <c r="G26">
         <v>961.5</v>
@@ -3419,45 +3419,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M26">
-        <v>182.4926544</v>
+        <v>198.69039</v>
       </c>
       <c r="N26">
-        <v>384.4399986612244</v>
+        <v>368.2422630612244</v>
       </c>
       <c r="O26">
-        <v>76.88799973224489</v>
+        <v>73.6484526122449</v>
       </c>
       <c r="P26">
-        <v>307.5519989289795</v>
+        <v>294.5938104489795</v>
       </c>
       <c r="Q26">
-        <v>1067.251998928979</v>
+        <v>1054.293810448979</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09259778777512589</v>
+        <v>0.09312213273619174</v>
       </c>
       <c r="T26">
-        <v>0.9121759884137839</v>
+        <v>0.9223964476677199</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.106605331185453</v>
+        <v>2.853347124947636</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08140159955214381</v>
+        <v>0.08133128039519193</v>
       </c>
       <c r="C27">
-        <v>9354.590892214106</v>
+        <v>9240.502647206553</v>
       </c>
       <c r="D27">
-        <v>11830.64089221411</v>
+        <v>11854.05464720655</v>
       </c>
       <c r="E27">
-        <v>-5153.25</v>
+        <v>-5015.748</v>
       </c>
       <c r="F27">
-        <v>3437.55</v>
+        <v>3575.052</v>
       </c>
       <c r="G27">
         <v>961.5</v>
@@ -3501,28 +3501,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M27">
-        <v>198.69039</v>
+        <v>206.6380056</v>
       </c>
       <c r="N27">
-        <v>368.2422630612244</v>
+        <v>360.2946474612244</v>
       </c>
       <c r="O27">
-        <v>73.6484526122449</v>
+        <v>72.05892949224489</v>
       </c>
       <c r="P27">
-        <v>294.5938104489795</v>
+        <v>288.2357179689795</v>
       </c>
       <c r="Q27">
-        <v>1054.293810448979</v>
+        <v>1047.93571796898</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09312213273619174</v>
+        <v>0.09366064918269179</v>
       </c>
       <c r="T27">
-        <v>0.9223964476677199</v>
+        <v>0.9328931355501406</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.853347124947636</v>
+        <v>2.743603004757342</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08133128039519193</v>
+        <v>0.08126096123824005</v>
       </c>
       <c r="C28">
-        <v>9240.502647206553</v>
+        <v>9126.507261244815</v>
       </c>
       <c r="D28">
-        <v>11854.05464720655</v>
+        <v>11877.56126124481</v>
       </c>
       <c r="E28">
-        <v>-5015.748</v>
+        <v>-4878.245999999999</v>
       </c>
       <c r="F28">
-        <v>3575.052</v>
+        <v>3712.554</v>
       </c>
       <c r="G28">
         <v>961.5</v>
@@ -3583,28 +3583,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M28">
-        <v>206.6380056</v>
+        <v>214.5856212</v>
       </c>
       <c r="N28">
-        <v>360.2946474612244</v>
+        <v>352.3470318612244</v>
       </c>
       <c r="O28">
-        <v>72.05892949224489</v>
+        <v>70.46940637224489</v>
       </c>
       <c r="P28">
-        <v>288.2357179689795</v>
+        <v>281.8776254889796</v>
       </c>
       <c r="Q28">
-        <v>1047.93571796898</v>
+        <v>1041.577625488979</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09366064918269179</v>
+        <v>0.09421391950443841</v>
       </c>
       <c r="T28">
-        <v>0.9328931355501406</v>
+        <v>0.9436774039224908</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.743603004757342</v>
+        <v>2.641988078655218</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08126096123824005</v>
+        <v>0.08119064208128818</v>
       </c>
       <c r="C29">
-        <v>9126.507261244815</v>
+        <v>9012.605287845532</v>
       </c>
       <c r="D29">
-        <v>11877.56126124481</v>
+        <v>11901.16128784553</v>
       </c>
       <c r="E29">
-        <v>-4878.245999999999</v>
+        <v>-4740.743999999999</v>
       </c>
       <c r="F29">
-        <v>3712.554</v>
+        <v>3850.056</v>
       </c>
       <c r="G29">
         <v>961.5</v>
@@ -3665,28 +3665,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M29">
-        <v>214.5856212</v>
+        <v>222.5332368</v>
       </c>
       <c r="N29">
-        <v>352.3470318612244</v>
+        <v>344.3994162612244</v>
       </c>
       <c r="O29">
-        <v>70.46940637224489</v>
+        <v>68.87988325224488</v>
       </c>
       <c r="P29">
-        <v>281.8776254889796</v>
+        <v>275.5195330089795</v>
       </c>
       <c r="Q29">
-        <v>1041.577625488979</v>
+        <v>1035.219533008979</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09421391950443841</v>
+        <v>0.09478255844623357</v>
       </c>
       <c r="T29">
-        <v>0.9436774039224908</v>
+        <v>0.9547612353051839</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.641988078655218</v>
+        <v>2.547631361560388</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08119064208128818</v>
+        <v>0.08193232292433628</v>
       </c>
       <c r="C30">
-        <v>9012.605287845532</v>
+        <v>8630.810570886682</v>
       </c>
       <c r="D30">
-        <v>11901.16128784553</v>
+        <v>11656.86857088668</v>
       </c>
       <c r="E30">
-        <v>-4740.743999999999</v>
+        <v>-4603.241999999999</v>
       </c>
       <c r="F30">
-        <v>3850.056</v>
+        <v>3987.558</v>
       </c>
       <c r="G30">
         <v>961.5</v>
@@ -3747,45 +3747,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M30">
-        <v>222.5332368</v>
+        <v>244.4373054</v>
       </c>
       <c r="N30">
-        <v>344.3994162612244</v>
+        <v>322.4953476612244</v>
       </c>
       <c r="O30">
-        <v>68.87988325224488</v>
+        <v>64.49906953224489</v>
       </c>
       <c r="P30">
-        <v>275.5195330089795</v>
+        <v>257.9962781289795</v>
       </c>
       <c r="Q30">
-        <v>1035.219533008979</v>
+        <v>1017.696278128979</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09478255844623357</v>
+        <v>0.09536721538638912</v>
       </c>
       <c r="T30">
-        <v>0.9547612353051839</v>
+        <v>0.9661572872902063</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.547631361560388</v>
+        <v>2.319337681020044</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08193232292433628</v>
+        <v>0.0825620037673844</v>
       </c>
       <c r="C31">
-        <v>8630.810570886684</v>
+        <v>8293.642990210983</v>
       </c>
       <c r="D31">
-        <v>11656.86857088668</v>
+        <v>11457.20299021098</v>
       </c>
       <c r="E31">
-        <v>-4603.242</v>
+        <v>-4465.74</v>
       </c>
       <c r="F31">
-        <v>3987.558</v>
+        <v>4125.059999999999</v>
       </c>
       <c r="G31">
         <v>961.5</v>
@@ -3829,45 +3829,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M31">
-        <v>244.4373054</v>
+        <v>264.416346</v>
       </c>
       <c r="N31">
-        <v>322.4953476612244</v>
+        <v>302.5163070612244</v>
       </c>
       <c r="O31">
-        <v>64.49906953224489</v>
+        <v>60.50326141224489</v>
       </c>
       <c r="P31">
-        <v>257.9962781289795</v>
+        <v>242.0130456489796</v>
       </c>
       <c r="Q31">
-        <v>1017.696278128979</v>
+        <v>1001.713045648979</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09536721538638912</v>
+        <v>0.09596857681054914</v>
       </c>
       <c r="T31">
-        <v>0.9661572872902063</v>
+        <v>0.9778789407605152</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.319337681020045</v>
+        <v>2.144090793317386</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0825620037673844</v>
+        <v>0.08254208461043251</v>
       </c>
       <c r="C32">
-        <v>8293.642990210983</v>
+        <v>8162.352336872756</v>
       </c>
       <c r="D32">
-        <v>11457.20299021098</v>
+        <v>11463.41433687276</v>
       </c>
       <c r="E32">
-        <v>-4465.74</v>
+        <v>-4328.237999999999</v>
       </c>
       <c r="F32">
-        <v>4125.059999999999</v>
+        <v>4262.562</v>
       </c>
       <c r="G32">
         <v>961.5</v>
@@ -3911,28 +3911,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M32">
-        <v>264.416346</v>
+        <v>273.2302242</v>
       </c>
       <c r="N32">
-        <v>302.5163070612244</v>
+        <v>293.7024288612244</v>
       </c>
       <c r="O32">
-        <v>60.50326141224489</v>
+        <v>58.74048577224488</v>
       </c>
       <c r="P32">
-        <v>242.0130456489796</v>
+        <v>234.9619430889795</v>
       </c>
       <c r="Q32">
-        <v>1001.713045648979</v>
+        <v>994.6619430889795</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09596857681054914</v>
+        <v>0.09658736900062684</v>
       </c>
       <c r="T32">
-        <v>0.9778789407605152</v>
+        <v>0.9899403523024272</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.144090793317386</v>
+        <v>2.074926574178115</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08254208461043251</v>
+        <v>0.08252216545348062</v>
       </c>
       <c r="C33">
-        <v>8162.352336872756</v>
+        <v>8031.068421960087</v>
       </c>
       <c r="D33">
-        <v>11463.41433687276</v>
+        <v>11469.63242196009</v>
       </c>
       <c r="E33">
-        <v>-4328.237999999999</v>
+        <v>-4190.736</v>
       </c>
       <c r="F33">
-        <v>4262.562</v>
+        <v>4400.063999999999</v>
       </c>
       <c r="G33">
         <v>961.5</v>
@@ -3993,28 +3993,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M33">
-        <v>273.2302242</v>
+        <v>282.0441024</v>
       </c>
       <c r="N33">
-        <v>293.7024288612244</v>
+        <v>284.8885506612244</v>
       </c>
       <c r="O33">
-        <v>58.74048577224488</v>
+        <v>56.97771013224489</v>
       </c>
       <c r="P33">
-        <v>234.9619430889795</v>
+        <v>227.9108405289795</v>
       </c>
       <c r="Q33">
-        <v>994.6619430889795</v>
+        <v>987.6108405289795</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09658736900062684</v>
+        <v>0.09722436096100093</v>
       </c>
       <c r="T33">
-        <v>0.9899403523024272</v>
+        <v>1.002356511242631</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.074926574178115</v>
+        <v>2.010085118735049</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08252216545348062</v>
+        <v>0.08559104629652875</v>
       </c>
       <c r="C34">
-        <v>8031.068421960087</v>
+        <v>7008.97205984532</v>
       </c>
       <c r="D34">
-        <v>11469.63242196009</v>
+        <v>10585.03805984532</v>
       </c>
       <c r="E34">
-        <v>-4190.736</v>
+        <v>-4053.233999999999</v>
       </c>
       <c r="F34">
-        <v>4400.063999999999</v>
+        <v>4537.566</v>
       </c>
       <c r="G34">
         <v>961.5</v>
@@ -4075,45 +4075,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M34">
-        <v>282.0441024</v>
+        <v>343.9475028</v>
       </c>
       <c r="N34">
-        <v>284.8885506612244</v>
+        <v>222.9851502612244</v>
       </c>
       <c r="O34">
-        <v>56.97771013224489</v>
+        <v>44.59703005224489</v>
       </c>
       <c r="P34">
-        <v>227.9108405289795</v>
+        <v>178.3881202089795</v>
       </c>
       <c r="Q34">
-        <v>987.6108405289795</v>
+        <v>938.0881202089795</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09722436096100093</v>
+        <v>0.09788036760675933</v>
       </c>
       <c r="T34">
-        <v>1.002356511242631</v>
+        <v>1.01514330179299</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05128000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.010085118735049</v>
+        <v>1.648311583732843</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08559104629652875</v>
+        <v>0.08566472713957686</v>
       </c>
       <c r="C35">
-        <v>7008.97205984532</v>
+        <v>6851.906034605286</v>
       </c>
       <c r="D35">
-        <v>10585.03805984532</v>
+        <v>10565.47403460529</v>
       </c>
       <c r="E35">
-        <v>-4053.233999999999</v>
+        <v>-3915.731999999999</v>
       </c>
       <c r="F35">
-        <v>4537.566</v>
+        <v>4675.068</v>
       </c>
       <c r="G35">
         <v>961.5</v>
@@ -4157,28 +4157,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M35">
-        <v>343.9475028</v>
+        <v>354.3701544</v>
       </c>
       <c r="N35">
-        <v>222.9851502612244</v>
+        <v>212.5624986612244</v>
       </c>
       <c r="O35">
-        <v>44.59703005224489</v>
+        <v>42.51249973224488</v>
       </c>
       <c r="P35">
-        <v>178.3881202089795</v>
+        <v>170.0499989289795</v>
       </c>
       <c r="Q35">
-        <v>938.0881202089795</v>
+        <v>929.7499989289795</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09788036760675933</v>
+        <v>0.09855625324178313</v>
       </c>
       <c r="T35">
-        <v>1.01514330179299</v>
+        <v>1.028317570844874</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.648311583732843</v>
+        <v>1.599831831270112</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08566472713957686</v>
+        <v>0.08573840798262498</v>
       </c>
       <c r="C36">
-        <v>6851.906034605286</v>
+        <v>6694.9121952107</v>
       </c>
       <c r="D36">
-        <v>10565.47403460529</v>
+        <v>10545.9821952107</v>
       </c>
       <c r="E36">
-        <v>-3915.731999999999</v>
+        <v>-3778.23</v>
       </c>
       <c r="F36">
-        <v>4675.068</v>
+        <v>4812.57</v>
       </c>
       <c r="G36">
         <v>961.5</v>
@@ -4239,28 +4239,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M36">
-        <v>354.3701544</v>
+        <v>364.792806</v>
       </c>
       <c r="N36">
-        <v>212.5624986612244</v>
+        <v>202.1398470612244</v>
       </c>
       <c r="O36">
-        <v>42.51249973224488</v>
+        <v>40.42796941224489</v>
       </c>
       <c r="P36">
-        <v>170.0499989289795</v>
+        <v>161.7118776489795</v>
       </c>
       <c r="Q36">
-        <v>929.7499989289795</v>
+        <v>921.4118776489795</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09855625324178313</v>
+        <v>0.0992529353578846</v>
       </c>
       <c r="T36">
-        <v>1.028317570844874</v>
+        <v>1.041897202021433</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.599831831270112</v>
+        <v>1.554122350376681</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08573840798262498</v>
+        <v>0.08581208882567311</v>
       </c>
       <c r="C37">
-        <v>6694.9121952107</v>
+        <v>6537.990142878538</v>
       </c>
       <c r="D37">
-        <v>10545.9821952107</v>
+        <v>10526.56214287854</v>
       </c>
       <c r="E37">
-        <v>-3778.23</v>
+        <v>-3640.727999999999</v>
       </c>
       <c r="F37">
-        <v>4812.57</v>
+        <v>4950.072</v>
       </c>
       <c r="G37">
         <v>961.5</v>
@@ -4321,28 +4321,28 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M37">
-        <v>364.792806</v>
+        <v>375.2154576</v>
       </c>
       <c r="N37">
-        <v>202.1398470612244</v>
+        <v>191.7171954612244</v>
       </c>
       <c r="O37">
-        <v>40.42796941224489</v>
+        <v>38.34343909224488</v>
       </c>
       <c r="P37">
-        <v>161.7118776489795</v>
+        <v>153.3737563689795</v>
       </c>
       <c r="Q37">
-        <v>921.4118776489795</v>
+        <v>913.0737563689795</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0992529353578846</v>
+        <v>0.09997138879011425</v>
       </c>
       <c r="T37">
-        <v>1.041897202021433</v>
+        <v>1.055901196672258</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.554122350376681</v>
+        <v>1.510952285088439</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08581208882567309</v>
+        <v>0.0992518205086276</v>
       </c>
       <c r="C38">
-        <v>6537.990142878544</v>
+        <v>3753.727576109838</v>
       </c>
       <c r="D38">
-        <v>10526.56214287854</v>
+        <v>7879.801576109838</v>
       </c>
       <c r="E38">
-        <v>-3640.728</v>
+        <v>-3503.226</v>
       </c>
       <c r="F38">
-        <v>4950.071999999999</v>
+        <v>5087.574</v>
       </c>
       <c r="G38">
         <v>961.5</v>
@@ -4403,45 +4403,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M38">
-        <v>375.2154576</v>
+        <v>603.3862764</v>
       </c>
       <c r="N38">
-        <v>191.7171954612244</v>
+        <v>-36.45362333877563</v>
       </c>
       <c r="O38">
-        <v>38.34343909224489</v>
+        <v>-7.290724667755126</v>
       </c>
       <c r="P38">
-        <v>153.3737563689795</v>
+        <v>-29.1628986710205</v>
       </c>
       <c r="Q38">
-        <v>913.0737563689795</v>
+        <v>730.5371013289795</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09997138879011422</v>
+        <v>0.1009777677773433</v>
       </c>
       <c r="T38">
-        <v>1.055901196672258</v>
+        <v>1.075517396305576</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.2</v>
+        <v>0.1879169862608511</v>
       </c>
       <c r="W38">
-        <v>0.06064000000000001</v>
+        <v>0.09631304542946308</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.510952285088439</v>
+        <v>0.9395849313042552</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0992518205086276</v>
+        <v>0.0999798205086276</v>
       </c>
       <c r="C39">
-        <v>3753.727576109838</v>
+        <v>3510.346754556814</v>
       </c>
       <c r="D39">
-        <v>7879.801576109838</v>
+        <v>7773.922754556814</v>
       </c>
       <c r="E39">
-        <v>-3503.226</v>
+        <v>-3365.723999999999</v>
       </c>
       <c r="F39">
-        <v>5087.574</v>
+        <v>5225.076</v>
       </c>
       <c r="G39">
         <v>961.5</v>
@@ -4485,37 +4485,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M39">
-        <v>603.3862764</v>
+        <v>619.6940136000001</v>
       </c>
       <c r="N39">
-        <v>-36.45362333877563</v>
+        <v>-52.76136053877565</v>
       </c>
       <c r="O39">
-        <v>-7.290724667755126</v>
+        <v>-10.55227210775513</v>
       </c>
       <c r="P39">
-        <v>-29.1628986710205</v>
+        <v>-42.20908843102052</v>
       </c>
       <c r="Q39">
-        <v>730.5371013289795</v>
+        <v>717.4909115689794</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1009777677773433</v>
+        <v>0.101867731773752</v>
       </c>
       <c r="T39">
-        <v>1.075517396305576</v>
+        <v>1.092864451084699</v>
       </c>
       <c r="U39">
         <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.1879169862608511</v>
+        <v>0.1829718024118813</v>
       </c>
       <c r="W39">
-        <v>0.09631304542946308</v>
+        <v>0.09689954423395089</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9395849313042552</v>
+        <v>0.9148590120594065</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0999798205086276</v>
+        <v>0.1007078205086276</v>
       </c>
       <c r="C40">
-        <v>3510.346754556814</v>
+        <v>3269.773539693566</v>
       </c>
       <c r="D40">
-        <v>7773.922754556814</v>
+        <v>7670.851539693566</v>
       </c>
       <c r="E40">
-        <v>-3365.723999999999</v>
+        <v>-3228.222</v>
       </c>
       <c r="F40">
-        <v>5225.076</v>
+        <v>5362.578</v>
       </c>
       <c r="G40">
         <v>961.5</v>
@@ -4567,37 +4567,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M40">
-        <v>619.6940136000001</v>
+        <v>636.0017508</v>
       </c>
       <c r="N40">
-        <v>-52.76136053877565</v>
+        <v>-69.06909773877555</v>
       </c>
       <c r="O40">
-        <v>-10.55227210775513</v>
+        <v>-13.81381954775511</v>
       </c>
       <c r="P40">
-        <v>-42.20908843102052</v>
+        <v>-55.25527819102044</v>
       </c>
       <c r="Q40">
-        <v>717.4909115689794</v>
+        <v>704.4447218089795</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.101867731773752</v>
+        <v>0.102786874917584</v>
       </c>
       <c r="T40">
-        <v>1.092864451084699</v>
+        <v>1.110780261758218</v>
       </c>
       <c r="U40">
         <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.1829718024118813</v>
+        <v>0.1782802177346536</v>
       </c>
       <c r="W40">
-        <v>0.09689954423395089</v>
+        <v>0.09745596617667009</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9148590120594065</v>
+        <v>0.8914010886732679</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1007078205086276</v>
+        <v>0.1014358205086276</v>
       </c>
       <c r="C41">
-        <v>3269.773539693566</v>
+        <v>3031.897718118833</v>
       </c>
       <c r="D41">
-        <v>7670.851539693566</v>
+        <v>7570.477718118833</v>
       </c>
       <c r="E41">
-        <v>-3228.222</v>
+        <v>-3090.719999999999</v>
       </c>
       <c r="F41">
-        <v>5362.578</v>
+        <v>5500.08</v>
       </c>
       <c r="G41">
         <v>961.5</v>
@@ -4649,37 +4649,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M41">
-        <v>636.0017508</v>
+        <v>652.3094880000001</v>
       </c>
       <c r="N41">
-        <v>-69.06909773877555</v>
+        <v>-85.37683493877569</v>
       </c>
       <c r="O41">
-        <v>-13.81381954775511</v>
+        <v>-17.07536698775514</v>
       </c>
       <c r="P41">
-        <v>-55.25527819102044</v>
+        <v>-68.30146795102056</v>
       </c>
       <c r="Q41">
-        <v>704.4447218089795</v>
+        <v>691.3985320489794</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.102786874917584</v>
+        <v>0.1037366561662104</v>
       </c>
       <c r="T41">
-        <v>1.110780261758218</v>
+        <v>1.129293266120855</v>
       </c>
       <c r="U41">
         <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.1782802177346536</v>
+        <v>0.1738232122912872</v>
       </c>
       <c r="W41">
-        <v>0.09745596617667009</v>
+        <v>0.09798456702225333</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8914010886732679</v>
+        <v>0.8691160614564361</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1014358205086276</v>
+        <v>0.1021638205086276</v>
       </c>
       <c r="C42">
-        <v>3031.897718118833</v>
+        <v>2796.614770534788</v>
       </c>
       <c r="D42">
-        <v>7570.477718118833</v>
+        <v>7472.696770534788</v>
       </c>
       <c r="E42">
-        <v>-3090.719999999999</v>
+        <v>-2953.217999999999</v>
       </c>
       <c r="F42">
-        <v>5500.08</v>
+        <v>5637.582</v>
       </c>
       <c r="G42">
         <v>961.5</v>
@@ -4731,37 +4731,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M42">
-        <v>652.3094880000001</v>
+        <v>668.6172252000001</v>
       </c>
       <c r="N42">
-        <v>-85.37683493877569</v>
+        <v>-101.6845721387757</v>
       </c>
       <c r="O42">
-        <v>-17.07536698775514</v>
+        <v>-20.33691442775514</v>
       </c>
       <c r="P42">
-        <v>-68.30146795102056</v>
+        <v>-81.34765771102056</v>
       </c>
       <c r="Q42">
-        <v>691.3985320489794</v>
+        <v>678.3523422889793</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1037366561662104</v>
+        <v>0.1047186333893665</v>
       </c>
       <c r="T42">
-        <v>1.129293266120855</v>
+        <v>1.148433829953412</v>
       </c>
       <c r="U42">
         <v>0.1186</v>
       </c>
       <c r="V42">
-        <v>0.1738232122912872</v>
+        <v>0.1695836217475973</v>
       </c>
       <c r="W42">
-        <v>0.09798456702225333</v>
+        <v>0.09848738246073498</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8691160614564361</v>
+        <v>0.8479181087379863</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1021638205086276</v>
+        <v>0.1028918205086276</v>
       </c>
       <c r="C43">
-        <v>2796.614770534788</v>
+        <v>2563.825508708424</v>
       </c>
       <c r="D43">
-        <v>7472.696770534788</v>
+        <v>7377.409508708424</v>
       </c>
       <c r="E43">
-        <v>-2953.217999999999</v>
+        <v>-2815.715999999999</v>
       </c>
       <c r="F43">
-        <v>5637.582</v>
+        <v>5775.084</v>
       </c>
       <c r="G43">
         <v>961.5</v>
@@ -4813,37 +4813,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M43">
-        <v>668.6172252000001</v>
+        <v>684.9249624</v>
       </c>
       <c r="N43">
-        <v>-101.6845721387757</v>
+        <v>-117.9923093387756</v>
       </c>
       <c r="O43">
-        <v>-20.33691442775514</v>
+        <v>-23.59846186775512</v>
       </c>
       <c r="P43">
-        <v>-81.34765771102056</v>
+        <v>-94.39384747102049</v>
       </c>
       <c r="Q43">
-        <v>678.3523422889793</v>
+        <v>665.3061525289794</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1047186333893665</v>
+        <v>0.1057344718960798</v>
       </c>
       <c r="T43">
-        <v>1.148433829953412</v>
+        <v>1.168234413228471</v>
       </c>
       <c r="U43">
         <v>0.1186</v>
       </c>
       <c r="V43">
-        <v>0.1695836217475973</v>
+        <v>0.1655459164678926</v>
       </c>
       <c r="W43">
-        <v>0.09848738246073498</v>
+        <v>0.09896625430690795</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8479181087379863</v>
+        <v>0.827729582339463</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1028918205086276</v>
+        <v>0.1036198205086276</v>
       </c>
       <c r="C44">
-        <v>2563.825508708427</v>
+        <v>2333.435739858671</v>
       </c>
       <c r="D44">
-        <v>7377.409508708426</v>
+        <v>7284.52173985867</v>
       </c>
       <c r="E44">
-        <v>-2815.716</v>
+        <v>-2678.214</v>
       </c>
       <c r="F44">
-        <v>5775.083999999999</v>
+        <v>5912.585999999999</v>
       </c>
       <c r="G44">
         <v>961.5</v>
@@ -4895,37 +4895,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M44">
-        <v>684.9249623999999</v>
+        <v>701.2326995999999</v>
       </c>
       <c r="N44">
-        <v>-117.9923093387755</v>
+        <v>-134.3000465387755</v>
       </c>
       <c r="O44">
-        <v>-23.5984618677551</v>
+        <v>-26.86000930775511</v>
       </c>
       <c r="P44">
-        <v>-94.39384747102039</v>
+        <v>-107.4400372310204</v>
       </c>
       <c r="Q44">
-        <v>665.3061525289795</v>
+        <v>652.2599627689796</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1057344718960797</v>
+        <v>0.1067859538591689</v>
       </c>
       <c r="T44">
-        <v>1.168234413228471</v>
+        <v>1.188729753811426</v>
       </c>
       <c r="U44">
         <v>0.1186</v>
       </c>
       <c r="V44">
-        <v>0.1655459164678926</v>
+        <v>0.1616960114337556</v>
       </c>
       <c r="W44">
-        <v>0.09896625430690795</v>
+        <v>0.09942285304395659</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8277295823394631</v>
+        <v>0.8084800571687779</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1036198205086276</v>
+        <v>0.1415791744359425</v>
       </c>
       <c r="C45">
-        <v>2333.435739858671</v>
+        <v>-691.079439602905</v>
       </c>
       <c r="D45">
-        <v>7284.52173985867</v>
+        <v>4397.508560397095</v>
       </c>
       <c r="E45">
-        <v>-2678.214</v>
+        <v>-2540.712</v>
       </c>
       <c r="F45">
-        <v>5912.585999999999</v>
+        <v>6050.088</v>
       </c>
       <c r="G45">
         <v>961.5</v>
@@ -4977,45 +4977,45 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M45">
-        <v>701.2326995999999</v>
+        <v>1214.8576704</v>
       </c>
       <c r="N45">
-        <v>-134.3000465387755</v>
+        <v>-647.9250173387755</v>
       </c>
       <c r="O45">
-        <v>-26.86000930775511</v>
+        <v>-129.5850034677551</v>
       </c>
       <c r="P45">
-        <v>-107.4400372310204</v>
+        <v>-518.3400138710205</v>
       </c>
       <c r="Q45">
-        <v>652.2599627689796</v>
+        <v>241.3599861289795</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1067859538591689</v>
+        <v>0.1097738350482878</v>
       </c>
       <c r="T45">
-        <v>1.188729753811426</v>
+        <v>1.246969119527688</v>
       </c>
       <c r="U45">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1616960114337556</v>
+        <v>0.09333318081196428</v>
       </c>
       <c r="W45">
-        <v>0.09942285304395659</v>
+        <v>0.1820586972929576</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8084800571687779</v>
+        <v>0.4666659040598213</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1415791744359425</v>
+        <v>0.1431291744359425</v>
       </c>
       <c r="C46">
-        <v>-691.079439602905</v>
+        <v>-898.6132497781928</v>
       </c>
       <c r="D46">
-        <v>4397.508560397095</v>
+        <v>4327.476750221806</v>
       </c>
       <c r="E46">
-        <v>-2540.712</v>
+        <v>-2403.21</v>
       </c>
       <c r="F46">
-        <v>6050.088</v>
+        <v>6187.589999999999</v>
       </c>
       <c r="G46">
         <v>961.5</v>
@@ -5059,37 +5059,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M46">
-        <v>1214.8576704</v>
+        <v>1242.468072</v>
       </c>
       <c r="N46">
-        <v>-647.9250173387755</v>
+        <v>-675.5354189387755</v>
       </c>
       <c r="O46">
-        <v>-129.5850034677551</v>
+        <v>-135.1070837877551</v>
       </c>
       <c r="P46">
-        <v>-518.3400138710205</v>
+        <v>-540.4283351510204</v>
       </c>
       <c r="Q46">
-        <v>241.3599861289795</v>
+        <v>219.2716648489795</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1097738350482878</v>
+        <v>0.1109369956855294</v>
       </c>
       <c r="T46">
-        <v>1.246969119527688</v>
+        <v>1.269641285337282</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.09333318081196428</v>
+        <v>0.09125911012725396</v>
       </c>
       <c r="W46">
-        <v>0.1820586972929576</v>
+        <v>0.1824751706864474</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4666659040598213</v>
+        <v>0.4562955506362698</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1431291744359425</v>
+        <v>0.1446791744359425</v>
       </c>
       <c r="C47">
-        <v>-898.6132497781928</v>
+        <v>-1103.951465049077</v>
       </c>
       <c r="D47">
-        <v>4327.476750221806</v>
+        <v>4259.640534950922</v>
       </c>
       <c r="E47">
-        <v>-2403.21</v>
+        <v>-2265.708</v>
       </c>
       <c r="F47">
-        <v>6187.589999999999</v>
+        <v>6325.092</v>
       </c>
       <c r="G47">
         <v>961.5</v>
@@ -5141,37 +5141,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M47">
-        <v>1242.468072</v>
+        <v>1270.0784736</v>
       </c>
       <c r="N47">
-        <v>-675.5354189387755</v>
+        <v>-703.1458205387756</v>
       </c>
       <c r="O47">
-        <v>-135.1070837877551</v>
+        <v>-140.6291641077551</v>
       </c>
       <c r="P47">
-        <v>-540.4283351510204</v>
+        <v>-562.5166564310205</v>
       </c>
       <c r="Q47">
-        <v>219.2716648489795</v>
+        <v>197.1833435689795</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1109369956855294</v>
+        <v>0.1121432363463726</v>
       </c>
       <c r="T47">
-        <v>1.269641285337282</v>
+        <v>1.293153160991676</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.09125911012725396</v>
+        <v>0.08927521642883539</v>
       </c>
       <c r="W47">
-        <v>0.1824751706864474</v>
+        <v>0.1828735365410899</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4562955506362698</v>
+        <v>0.4463760821441769</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1446791744359425</v>
+        <v>0.1462291744359425</v>
       </c>
       <c r="C48">
-        <v>-1103.951465049077</v>
+        <v>-1307.195744284732</v>
       </c>
       <c r="D48">
-        <v>4259.640534950922</v>
+        <v>4193.898255715269</v>
       </c>
       <c r="E48">
-        <v>-2265.708</v>
+        <v>-2128.205999999999</v>
       </c>
       <c r="F48">
-        <v>6325.092</v>
+        <v>6462.594</v>
       </c>
       <c r="G48">
         <v>961.5</v>
@@ -5223,37 +5223,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M48">
-        <v>1270.0784736</v>
+        <v>1297.6888752</v>
       </c>
       <c r="N48">
-        <v>-703.1458205387756</v>
+        <v>-730.7562221387756</v>
       </c>
       <c r="O48">
-        <v>-140.6291641077551</v>
+        <v>-146.1512444277551</v>
       </c>
       <c r="P48">
-        <v>-562.5166564310205</v>
+        <v>-584.6049777110204</v>
       </c>
       <c r="Q48">
-        <v>197.1833435689795</v>
+        <v>175.0950222889795</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1121432363463726</v>
+        <v>0.1133949955227193</v>
       </c>
       <c r="T48">
-        <v>1.293153160991676</v>
+        <v>1.317552277236802</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.08927521642883539</v>
+        <v>0.08737574373886016</v>
       </c>
       <c r="W48">
-        <v>0.1828735365410899</v>
+        <v>0.1832549506572369</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4463760821441769</v>
+        <v>0.4368787186943008</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1462291744359425</v>
+        <v>0.1477791744359425</v>
       </c>
       <c r="C49">
-        <v>-1307.195744284732</v>
+        <v>-1508.441565827844</v>
       </c>
       <c r="D49">
-        <v>4193.898255715269</v>
+        <v>4130.154434172156</v>
       </c>
       <c r="E49">
-        <v>-2128.205999999999</v>
+        <v>-1990.704</v>
       </c>
       <c r="F49">
-        <v>6462.594</v>
+        <v>6600.096</v>
       </c>
       <c r="G49">
         <v>961.5</v>
@@ -5305,37 +5305,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M49">
-        <v>1297.6888752</v>
+        <v>1325.2992768</v>
       </c>
       <c r="N49">
-        <v>-730.7562221387756</v>
+        <v>-758.3666237387755</v>
       </c>
       <c r="O49">
-        <v>-146.1512444277551</v>
+        <v>-151.6733247477551</v>
       </c>
       <c r="P49">
-        <v>-584.6049777110204</v>
+        <v>-606.6932989910204</v>
       </c>
       <c r="Q49">
-        <v>175.0950222889795</v>
+        <v>153.0067010089796</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1133949955227193</v>
+        <v>0.1146948992827715</v>
       </c>
       <c r="T49">
-        <v>1.317552277236802</v>
+        <v>1.342889821029818</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.08737574373886016</v>
+        <v>0.08555541574430059</v>
       </c>
       <c r="W49">
-        <v>0.1832549506572369</v>
+        <v>0.1836204725185444</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4368787186943008</v>
+        <v>0.4277770787215029</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1477791744359425</v>
+        <v>0.1493291744359425</v>
       </c>
       <c r="C50">
-        <v>-1508.441565827842</v>
+        <v>-1707.778690157244</v>
       </c>
       <c r="D50">
-        <v>4130.154434172157</v>
+        <v>4068.319309842755</v>
       </c>
       <c r="E50">
-        <v>-1990.704</v>
+        <v>-1853.202</v>
       </c>
       <c r="F50">
-        <v>6600.096</v>
+        <v>6737.597999999999</v>
       </c>
       <c r="G50">
         <v>961.5</v>
@@ -5387,37 +5387,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M50">
-        <v>1325.2992768</v>
+        <v>1352.9096784</v>
       </c>
       <c r="N50">
-        <v>-758.3666237387755</v>
+        <v>-785.9770253387754</v>
       </c>
       <c r="O50">
-        <v>-151.6733247477551</v>
+        <v>-157.1954050677551</v>
       </c>
       <c r="P50">
-        <v>-606.6932989910204</v>
+        <v>-628.7816202710203</v>
       </c>
       <c r="Q50">
-        <v>153.0067010089796</v>
+        <v>130.9183797289796</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1146948992827715</v>
+        <v>0.1160457796608651</v>
       </c>
       <c r="T50">
-        <v>1.342889821029818</v>
+        <v>1.369220993991187</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.08555541574430059</v>
+        <v>0.08380938685155975</v>
       </c>
       <c r="W50">
-        <v>0.1836204725185444</v>
+        <v>0.1839710751202068</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4277770787215029</v>
+        <v>0.4190469342577988</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1493291744359425</v>
+        <v>0.1508791744359425</v>
       </c>
       <c r="C51">
-        <v>-1707.778690157244</v>
+        <v>-1905.291581602728</v>
       </c>
       <c r="D51">
-        <v>4068.319309842755</v>
+        <v>4008.308418397272</v>
       </c>
       <c r="E51">
-        <v>-1853.202</v>
+        <v>-1715.7</v>
       </c>
       <c r="F51">
-        <v>6737.597999999999</v>
+        <v>6875.099999999999</v>
       </c>
       <c r="G51">
         <v>961.5</v>
@@ -5469,37 +5469,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M51">
-        <v>1352.9096784</v>
+        <v>1380.52008</v>
       </c>
       <c r="N51">
-        <v>-785.9770253387754</v>
+        <v>-813.5874269387756</v>
       </c>
       <c r="O51">
-        <v>-157.1954050677551</v>
+        <v>-162.7174853877551</v>
       </c>
       <c r="P51">
-        <v>-628.7816202710203</v>
+        <v>-650.8699415510205</v>
       </c>
       <c r="Q51">
-        <v>130.9183797289796</v>
+        <v>108.8300584489795</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1160457796608651</v>
+        <v>0.1174506952540824</v>
       </c>
       <c r="T51">
-        <v>1.369220993991187</v>
+        <v>1.39660541387101</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.08380938685155975</v>
+        <v>0.08213319911452856</v>
       </c>
       <c r="W51">
-        <v>0.1839710751202068</v>
+        <v>0.1843076536178027</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4190469342577988</v>
+        <v>0.4106659955726427</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1508791744359425</v>
+        <v>0.1524291744359425</v>
       </c>
       <c r="C52">
-        <v>-1905.291581602728</v>
+        <v>-2101.059793278672</v>
       </c>
       <c r="D52">
-        <v>4008.308418397272</v>
+        <v>3950.042206721328</v>
       </c>
       <c r="E52">
-        <v>-1715.7</v>
+        <v>-1578.197999999999</v>
       </c>
       <c r="F52">
-        <v>6875.099999999999</v>
+        <v>7012.602</v>
       </c>
       <c r="G52">
         <v>961.5</v>
@@ -5551,37 +5551,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M52">
-        <v>1380.52008</v>
+        <v>1408.1304816</v>
       </c>
       <c r="N52">
-        <v>-813.5874269387756</v>
+        <v>-841.1978285387755</v>
       </c>
       <c r="O52">
-        <v>-162.7174853877551</v>
+        <v>-168.2395657077551</v>
       </c>
       <c r="P52">
-        <v>-650.8699415510205</v>
+        <v>-672.9582628310204</v>
       </c>
       <c r="Q52">
-        <v>108.8300584489795</v>
+        <v>86.74173716897951</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1174506952540824</v>
+        <v>0.1189129543409004</v>
       </c>
       <c r="T52">
-        <v>1.39660541387101</v>
+        <v>1.4251075651745</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.08213319911452856</v>
+        <v>0.08052274422992996</v>
       </c>
       <c r="W52">
-        <v>0.1843076536178027</v>
+        <v>0.1846310329586301</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4106659955726427</v>
+        <v>0.4026137211496498</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1524291744359425</v>
+        <v>0.1539791744359426</v>
       </c>
       <c r="C53">
-        <v>-2101.059793278672</v>
+        <v>-2295.158318925515</v>
       </c>
       <c r="D53">
-        <v>3950.042206721328</v>
+        <v>3893.445681074484</v>
       </c>
       <c r="E53">
-        <v>-1578.197999999999</v>
+        <v>-1440.696</v>
       </c>
       <c r="F53">
-        <v>7012.602</v>
+        <v>7150.103999999999</v>
       </c>
       <c r="G53">
         <v>961.5</v>
@@ -5633,37 +5633,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M53">
-        <v>1408.1304816</v>
+        <v>1435.7408832</v>
       </c>
       <c r="N53">
-        <v>-841.1978285387755</v>
+        <v>-868.8082301387755</v>
       </c>
       <c r="O53">
-        <v>-168.2395657077551</v>
+        <v>-173.7616460277551</v>
       </c>
       <c r="P53">
-        <v>-672.9582628310204</v>
+        <v>-695.0465841110204</v>
       </c>
       <c r="Q53">
-        <v>86.74173716897951</v>
+        <v>64.65341588897957</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1189129543409004</v>
+        <v>0.1204361408896692</v>
       </c>
       <c r="T53">
-        <v>1.4251075651745</v>
+        <v>1.454797306115636</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.08052274422992996</v>
+        <v>0.07897422991781593</v>
       </c>
       <c r="W53">
-        <v>0.1846310329586301</v>
+        <v>0.1849419746325026</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4026137211496498</v>
+        <v>0.3948711495890797</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1539791744359426</v>
+        <v>0.1555291744359426</v>
       </c>
       <c r="C54">
-        <v>-2295.158318925515</v>
+        <v>-2487.657914931201</v>
       </c>
       <c r="D54">
-        <v>3893.445681074484</v>
+        <v>3838.448085068799</v>
       </c>
       <c r="E54">
-        <v>-1440.696</v>
+        <v>-1303.194</v>
       </c>
       <c r="F54">
-        <v>7150.103999999999</v>
+        <v>7287.606</v>
       </c>
       <c r="G54">
         <v>961.5</v>
@@ -5715,37 +5715,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M54">
-        <v>1435.7408832</v>
+        <v>1463.3512848</v>
       </c>
       <c r="N54">
-        <v>-868.8082301387755</v>
+        <v>-896.4186317387756</v>
       </c>
       <c r="O54">
-        <v>-173.7616460277551</v>
+        <v>-179.2837263477551</v>
       </c>
       <c r="P54">
-        <v>-695.0465841110204</v>
+        <v>-717.1349053910205</v>
       </c>
       <c r="Q54">
-        <v>64.65341588897957</v>
+        <v>42.56509460897939</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1204361408896692</v>
+        <v>0.1220241438873217</v>
       </c>
       <c r="T54">
-        <v>1.454797306115636</v>
+        <v>1.485750440288309</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.07897422991781593</v>
+        <v>0.07748415010804581</v>
       </c>
       <c r="W54">
-        <v>0.1849419746325026</v>
+        <v>0.1852411826583044</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3948711495890797</v>
+        <v>0.387420750540229</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1555291744359426</v>
+        <v>0.1570791744359425</v>
       </c>
       <c r="C55">
-        <v>-2487.657914931201</v>
+        <v>-2678.625395440149</v>
       </c>
       <c r="D55">
-        <v>3838.448085068799</v>
+        <v>3784.982604559852</v>
       </c>
       <c r="E55">
-        <v>-1303.194</v>
+        <v>-1165.691999999999</v>
       </c>
       <c r="F55">
-        <v>7287.606</v>
+        <v>7425.108</v>
       </c>
       <c r="G55">
         <v>961.5</v>
@@ -5797,37 +5797,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M55">
-        <v>1463.3512848</v>
+        <v>1490.9616864</v>
       </c>
       <c r="N55">
-        <v>-896.4186317387756</v>
+        <v>-924.0290333387758</v>
       </c>
       <c r="O55">
-        <v>-179.2837263477551</v>
+        <v>-184.8058066677552</v>
       </c>
       <c r="P55">
-        <v>-717.1349053910205</v>
+        <v>-739.2232266710206</v>
       </c>
       <c r="Q55">
-        <v>42.56509460897939</v>
+        <v>20.47677332897933</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1220241438873217</v>
+        <v>0.1236811904935678</v>
       </c>
       <c r="T55">
-        <v>1.485750440288309</v>
+        <v>1.518049362903272</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.07748415010804581</v>
+        <v>0.07604925843937828</v>
       </c>
       <c r="W55">
-        <v>0.1852411826583044</v>
+        <v>0.1855293089053729</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.387420750540229</v>
+        <v>0.3802462921968914</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1570791744359425</v>
+        <v>0.1586291744359425</v>
       </c>
       <c r="C56">
-        <v>-2678.625395440149</v>
+        <v>-2868.123903137708</v>
       </c>
       <c r="D56">
-        <v>3784.982604559852</v>
+        <v>3732.986096862292</v>
       </c>
       <c r="E56">
-        <v>-1165.691999999999</v>
+        <v>-1028.19</v>
       </c>
       <c r="F56">
-        <v>7425.108</v>
+        <v>7562.61</v>
       </c>
       <c r="G56">
         <v>961.5</v>
@@ -5879,37 +5879,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M56">
-        <v>1490.9616864</v>
+        <v>1518.572088</v>
       </c>
       <c r="N56">
-        <v>-924.0290333387758</v>
+        <v>-951.6394349387755</v>
       </c>
       <c r="O56">
-        <v>-184.8058066677552</v>
+        <v>-190.3278869877551</v>
       </c>
       <c r="P56">
-        <v>-739.2232266710206</v>
+        <v>-761.3115479510204</v>
       </c>
       <c r="Q56">
-        <v>20.47677332897933</v>
+        <v>-1.611547951020498</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1236811904935678</v>
+        <v>0.1254118836156471</v>
       </c>
       <c r="T56">
-        <v>1.518049362903272</v>
+        <v>1.551783793190012</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07604925843937828</v>
+        <v>0.07466654464957141</v>
       </c>
       <c r="W56">
-        <v>0.1855293089053729</v>
+        <v>0.1858069578343661</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3802462921968914</v>
+        <v>0.373332723247857</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1586291744359425</v>
+        <v>0.1601791744359425</v>
       </c>
       <c r="C57">
-        <v>-2868.123903137708</v>
+        <v>-3056.213158017546</v>
       </c>
       <c r="D57">
-        <v>3732.986096862292</v>
+        <v>3682.398841982454</v>
       </c>
       <c r="E57">
-        <v>-1028.19</v>
+        <v>-890.6879999999992</v>
       </c>
       <c r="F57">
-        <v>7562.61</v>
+        <v>7700.112</v>
       </c>
       <c r="G57">
         <v>961.5</v>
@@ -5961,37 +5961,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M57">
-        <v>1518.572088</v>
+        <v>1546.1824896</v>
       </c>
       <c r="N57">
-        <v>-951.6394349387755</v>
+        <v>-979.2498365387756</v>
       </c>
       <c r="O57">
-        <v>-190.3278869877551</v>
+        <v>-195.8499673077552</v>
       </c>
       <c r="P57">
-        <v>-761.3115479510204</v>
+        <v>-783.3998692310205</v>
       </c>
       <c r="Q57">
-        <v>-1.611547951020498</v>
+        <v>-23.69986923102056</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1254118836156471</v>
+        <v>0.1272212446069118</v>
       </c>
       <c r="T57">
-        <v>1.551783793190012</v>
+        <v>1.587051606671603</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.07466654464957141</v>
+        <v>0.07333321349511478</v>
       </c>
       <c r="W57">
-        <v>0.1858069578343661</v>
+        <v>0.186074690730181</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.373332723247857</v>
+        <v>0.3666660674755738</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1601791744359425</v>
+        <v>0.1617291744359425</v>
       </c>
       <c r="C58">
-        <v>-3056.213158017546</v>
+        <v>-3242.949686192563</v>
       </c>
       <c r="D58">
-        <v>3682.398841982454</v>
+        <v>3633.164313807438</v>
       </c>
       <c r="E58">
-        <v>-890.6879999999992</v>
+        <v>-753.1859999999988</v>
       </c>
       <c r="F58">
-        <v>7700.112</v>
+        <v>7837.614</v>
       </c>
       <c r="G58">
         <v>961.5</v>
@@ -6043,37 +6043,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M58">
-        <v>1546.1824896</v>
+        <v>1573.7928912</v>
       </c>
       <c r="N58">
-        <v>-979.2498365387756</v>
+        <v>-1006.860238138776</v>
       </c>
       <c r="O58">
-        <v>-195.8499673077552</v>
+        <v>-201.3720476277552</v>
       </c>
       <c r="P58">
-        <v>-783.3998692310205</v>
+        <v>-805.4881905110207</v>
       </c>
       <c r="Q58">
-        <v>-23.69986923102056</v>
+        <v>-45.78819051102073</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1272212446069118</v>
+        <v>0.1291147619233516</v>
       </c>
       <c r="T58">
-        <v>1.587051606671603</v>
+        <v>1.623959783570943</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.07333321349511478</v>
+        <v>0.07204666588993731</v>
       </c>
       <c r="W58">
-        <v>0.186074690730181</v>
+        <v>0.1863330294893006</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3666660674755738</v>
+        <v>0.3602333294496866</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1617291744359425</v>
+        <v>0.1632791744359425</v>
       </c>
       <c r="C59">
-        <v>-3242.949686192563</v>
+        <v>-3428.38703059245</v>
       </c>
       <c r="D59">
-        <v>3633.164313807438</v>
+        <v>3585.228969407549</v>
       </c>
       <c r="E59">
-        <v>-753.1859999999988</v>
+        <v>-615.6839999999993</v>
       </c>
       <c r="F59">
-        <v>7837.614</v>
+        <v>7975.116</v>
       </c>
       <c r="G59">
         <v>961.5</v>
@@ -6125,37 +6125,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M59">
-        <v>1573.7928912</v>
+        <v>1601.4032928</v>
       </c>
       <c r="N59">
-        <v>-1006.860238138776</v>
+        <v>-1034.470639738776</v>
       </c>
       <c r="O59">
-        <v>-201.3720476277552</v>
+        <v>-206.8941279477552</v>
       </c>
       <c r="P59">
-        <v>-805.4881905110207</v>
+        <v>-827.5765117910207</v>
       </c>
       <c r="Q59">
-        <v>-45.78819051102073</v>
+        <v>-67.87651179102079</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1291147619233516</v>
+        <v>0.1310984467310505</v>
       </c>
       <c r="T59">
-        <v>1.623959783570943</v>
+        <v>1.662625492703584</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.07204666588993731</v>
+        <v>0.07080448199528323</v>
       </c>
       <c r="W59">
-        <v>0.1863330294893006</v>
+        <v>0.1865824600153471</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3602333294496866</v>
+        <v>0.3540224099764161</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1632791744359425</v>
+        <v>0.1648291744359425</v>
       </c>
       <c r="C60">
-        <v>-3428.387030592449</v>
+        <v>-3612.575945199022</v>
       </c>
       <c r="D60">
-        <v>3585.228969407549</v>
+        <v>3538.542054800976</v>
       </c>
       <c r="E60">
-        <v>-615.6840000000002</v>
+        <v>-478.1820000000007</v>
       </c>
       <c r="F60">
-        <v>7975.115999999999</v>
+        <v>8112.617999999999</v>
       </c>
       <c r="G60">
         <v>961.5</v>
@@ -6207,37 +6207,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M60">
-        <v>1601.4032928</v>
+        <v>1629.0136944</v>
       </c>
       <c r="N60">
-        <v>-1034.470639738775</v>
+        <v>-1062.081041338775</v>
       </c>
       <c r="O60">
-        <v>-206.8941279477551</v>
+        <v>-212.4162082677551</v>
       </c>
       <c r="P60">
-        <v>-827.5765117910203</v>
+        <v>-849.6648330710202</v>
       </c>
       <c r="Q60">
-        <v>-67.87651179102033</v>
+        <v>-89.96483307102028</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1310984467310504</v>
+        <v>0.13317889665132</v>
       </c>
       <c r="T60">
-        <v>1.662625492703584</v>
+        <v>1.703177333989037</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07080448199528325</v>
+        <v>0.06960440602926149</v>
       </c>
       <c r="W60">
-        <v>0.1865824600153471</v>
+        <v>0.1868234352693243</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3540224099764162</v>
+        <v>0.3480220301463075</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1648291744359425</v>
+        <v>0.1663791744359426</v>
       </c>
       <c r="C61">
-        <v>-3612.575945199022</v>
+        <v>-3795.564574300596</v>
       </c>
       <c r="D61">
-        <v>3538.542054800976</v>
+        <v>3493.055425699403</v>
       </c>
       <c r="E61">
-        <v>-478.1820000000007</v>
+        <v>-340.6800000000003</v>
       </c>
       <c r="F61">
-        <v>8112.617999999999</v>
+        <v>8250.119999999999</v>
       </c>
       <c r="G61">
         <v>961.5</v>
@@ -6289,37 +6289,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M61">
-        <v>1629.0136944</v>
+        <v>1656.624096</v>
       </c>
       <c r="N61">
-        <v>-1062.081041338775</v>
+        <v>-1089.691442938775</v>
       </c>
       <c r="O61">
-        <v>-212.4162082677551</v>
+        <v>-217.9382885877551</v>
       </c>
       <c r="P61">
-        <v>-849.6648330710202</v>
+        <v>-871.7531543510202</v>
       </c>
       <c r="Q61">
-        <v>-89.96483307102028</v>
+        <v>-112.0531543510202</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.13317889665132</v>
+        <v>0.135363369067603</v>
       </c>
       <c r="T61">
-        <v>1.703177333989037</v>
+        <v>1.745756767338763</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06960440602926149</v>
+        <v>0.06844433259544047</v>
       </c>
       <c r="W61">
-        <v>0.1868234352693243</v>
+        <v>0.1870563780148356</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3480220301463075</v>
+        <v>0.3422216629772024</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1663791744359426</v>
+        <v>0.1679291744359425</v>
       </c>
       <c r="C62">
-        <v>-3795.564574300596</v>
+        <v>-3977.398618096355</v>
       </c>
       <c r="D62">
-        <v>3493.055425699403</v>
+        <v>3448.723381903644</v>
       </c>
       <c r="E62">
-        <v>-340.6800000000003</v>
+        <v>-203.1779999999999</v>
       </c>
       <c r="F62">
-        <v>8250.119999999999</v>
+        <v>8387.621999999999</v>
       </c>
       <c r="G62">
         <v>961.5</v>
@@ -6371,37 +6371,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M62">
-        <v>1656.624096</v>
+        <v>1684.2344976</v>
       </c>
       <c r="N62">
-        <v>-1089.691442938775</v>
+        <v>-1117.301844538776</v>
       </c>
       <c r="O62">
-        <v>-217.9382885877551</v>
+        <v>-223.4603689077551</v>
       </c>
       <c r="P62">
-        <v>-871.7531543510202</v>
+        <v>-893.8414756310206</v>
       </c>
       <c r="Q62">
-        <v>-112.0531543510202</v>
+        <v>-134.1414756310206</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.135363369067603</v>
+        <v>0.137659865710362</v>
       </c>
       <c r="T62">
-        <v>1.745756767338763</v>
+        <v>1.79051976137309</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06844433259544047</v>
+        <v>0.06732229435617094</v>
       </c>
       <c r="W62">
-        <v>0.1870563780148356</v>
+        <v>0.1872816832932809</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3422216629772024</v>
+        <v>0.3366114717808547</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1679291744359425</v>
+        <v>0.1694791744359425</v>
       </c>
       <c r="C63">
-        <v>-3977.398618096355</v>
+        <v>-4158.121485848179</v>
       </c>
       <c r="D63">
-        <v>3448.723381903644</v>
+        <v>3405.502514151821</v>
       </c>
       <c r="E63">
-        <v>-203.1779999999999</v>
+        <v>-65.67599999999948</v>
       </c>
       <c r="F63">
-        <v>8387.621999999999</v>
+        <v>8525.124</v>
       </c>
       <c r="G63">
         <v>961.5</v>
@@ -6453,37 +6453,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M63">
-        <v>1684.2344976</v>
+        <v>1711.8448992</v>
       </c>
       <c r="N63">
-        <v>-1117.301844538776</v>
+        <v>-1144.912246138776</v>
       </c>
       <c r="O63">
-        <v>-223.4603689077551</v>
+        <v>-228.9824492277551</v>
       </c>
       <c r="P63">
-        <v>-893.8414756310206</v>
+        <v>-915.9297969110205</v>
       </c>
       <c r="Q63">
-        <v>-134.1414756310206</v>
+        <v>-156.2297969110206</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.137659865710362</v>
+        <v>0.1400772305974768</v>
       </c>
       <c r="T63">
-        <v>1.79051976137309</v>
+        <v>1.837638702461856</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.06732229435617094</v>
+        <v>0.06623645089881335</v>
       </c>
       <c r="W63">
-        <v>0.1872816832932809</v>
+        <v>0.1874997206595183</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3366114717808547</v>
+        <v>0.3311822544940668</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1694791744359425</v>
+        <v>0.1710291744359425</v>
       </c>
       <c r="C64">
-        <v>-4158.121485848179</v>
+        <v>-4337.774437658818</v>
       </c>
       <c r="D64">
-        <v>3405.502514151821</v>
+        <v>3363.351562341182</v>
       </c>
       <c r="E64">
-        <v>-65.67599999999948</v>
+        <v>71.82600000000093</v>
       </c>
       <c r="F64">
-        <v>8525.124</v>
+        <v>8662.626</v>
       </c>
       <c r="G64">
         <v>961.5</v>
@@ -6535,37 +6535,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M64">
-        <v>1711.8448992</v>
+        <v>1739.4553008</v>
       </c>
       <c r="N64">
-        <v>-1144.912246138776</v>
+        <v>-1172.522647738776</v>
       </c>
       <c r="O64">
-        <v>-228.9824492277551</v>
+        <v>-234.5045295477551</v>
       </c>
       <c r="P64">
-        <v>-915.9297969110205</v>
+        <v>-938.0181181910204</v>
       </c>
       <c r="Q64">
-        <v>-156.2297969110206</v>
+        <v>-178.3181181910205</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1400772305974768</v>
+        <v>0.1426252638568681</v>
       </c>
       <c r="T64">
-        <v>1.837638702461856</v>
+        <v>1.887304613339203</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06623645089881335</v>
+        <v>0.06518507866232424</v>
       </c>
       <c r="W64">
-        <v>0.1874997206595183</v>
+        <v>0.1877108362046053</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3311822544940668</v>
+        <v>0.3259253933116213</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1710291744359425</v>
+        <v>0.1725791744359425</v>
       </c>
       <c r="C65">
-        <v>-4337.774437658818</v>
+        <v>-4516.396715849796</v>
       </c>
       <c r="D65">
-        <v>3363.351562341182</v>
+        <v>3322.231284150203</v>
       </c>
       <c r="E65">
-        <v>71.82600000000093</v>
+        <v>209.3279999999995</v>
       </c>
       <c r="F65">
-        <v>8662.626</v>
+        <v>8800.127999999999</v>
       </c>
       <c r="G65">
         <v>961.5</v>
@@ -6617,37 +6617,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M65">
-        <v>1739.4553008</v>
+        <v>1767.0657024</v>
       </c>
       <c r="N65">
-        <v>-1172.522647738776</v>
+        <v>-1200.133049338775</v>
       </c>
       <c r="O65">
-        <v>-234.5045295477551</v>
+        <v>-240.0266098677551</v>
       </c>
       <c r="P65">
-        <v>-938.0181181910204</v>
+        <v>-960.1064394710204</v>
       </c>
       <c r="Q65">
-        <v>-178.3181181910205</v>
+        <v>-200.4064394710205</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1426252638568681</v>
+        <v>0.1453148545195589</v>
       </c>
       <c r="T65">
-        <v>1.887304613339203</v>
+        <v>1.939729741487515</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.06518507866232424</v>
+        <v>0.06416656180822544</v>
       </c>
       <c r="W65">
-        <v>0.1877108362046053</v>
+        <v>0.1879153543889083</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3259253933116213</v>
+        <v>0.3208328090411271</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1725791744359425</v>
+        <v>0.1741291744359426</v>
       </c>
       <c r="C66">
-        <v>-4516.396715849796</v>
+        <v>-4694.025666818404</v>
       </c>
       <c r="D66">
-        <v>3322.231284150203</v>
+        <v>3282.104333181595</v>
       </c>
       <c r="E66">
-        <v>209.3279999999995</v>
+        <v>346.8299999999999</v>
       </c>
       <c r="F66">
-        <v>8800.127999999999</v>
+        <v>8937.629999999999</v>
       </c>
       <c r="G66">
         <v>961.5</v>
@@ -6699,37 +6699,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M66">
-        <v>1767.0657024</v>
+        <v>1794.676104</v>
       </c>
       <c r="N66">
-        <v>-1200.133049338775</v>
+        <v>-1227.743450938775</v>
       </c>
       <c r="O66">
-        <v>-240.0266098677551</v>
+        <v>-245.5486901877551</v>
       </c>
       <c r="P66">
-        <v>-960.1064394710204</v>
+        <v>-982.1947607510203</v>
       </c>
       <c r="Q66">
-        <v>-200.4064394710205</v>
+        <v>-222.4947607510204</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1453148545195589</v>
+        <v>0.1481581360772606</v>
       </c>
       <c r="T66">
-        <v>1.939729741487515</v>
+        <v>1.995150591244301</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.06416656180822544</v>
+        <v>0.06317938393425274</v>
       </c>
       <c r="W66">
-        <v>0.1879153543889083</v>
+        <v>0.1881135797060021</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3208328090411271</v>
+        <v>0.3158969196712638</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1741291744359426</v>
+        <v>0.1756791744359426</v>
       </c>
       <c r="C67">
-        <v>-4694.025666818404</v>
+        <v>-4870.696854169071</v>
       </c>
       <c r="D67">
-        <v>3282.104333181595</v>
+        <v>3242.935145830928</v>
       </c>
       <c r="E67">
-        <v>346.8299999999999</v>
+        <v>484.3320000000003</v>
       </c>
       <c r="F67">
-        <v>8937.629999999999</v>
+        <v>9075.132</v>
       </c>
       <c r="G67">
         <v>961.5</v>
@@ -6781,37 +6781,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M67">
-        <v>1794.676104</v>
+        <v>1822.2865056</v>
       </c>
       <c r="N67">
-        <v>-1227.743450938775</v>
+        <v>-1255.353852538776</v>
       </c>
       <c r="O67">
-        <v>-245.5486901877551</v>
+        <v>-251.0707705077552</v>
       </c>
       <c r="P67">
-        <v>-982.1947607510203</v>
+        <v>-1004.283082031021</v>
       </c>
       <c r="Q67">
-        <v>-222.4947607510204</v>
+        <v>-244.5830820310207</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1481581360772606</v>
+        <v>0.1511686694912976</v>
       </c>
       <c r="T67">
-        <v>1.995150591244301</v>
+        <v>2.05383149098678</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.06317938393425274</v>
+        <v>0.0622221205413095</v>
       </c>
       <c r="W67">
-        <v>0.1881135797060021</v>
+        <v>0.1883057981953051</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3158969196712638</v>
+        <v>0.3111106027065474</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1756791744359426</v>
+        <v>0.1772291744359425</v>
       </c>
       <c r="C68">
-        <v>-4870.696854169071</v>
+        <v>-5046.444163839549</v>
       </c>
       <c r="D68">
-        <v>3242.935145830928</v>
+        <v>3204.689836160451</v>
       </c>
       <c r="E68">
-        <v>484.3320000000003</v>
+        <v>621.8340000000007</v>
       </c>
       <c r="F68">
-        <v>9075.132</v>
+        <v>9212.634</v>
       </c>
       <c r="G68">
         <v>961.5</v>
@@ -6863,37 +6863,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M68">
-        <v>1822.2865056</v>
+        <v>1849.8969072</v>
       </c>
       <c r="N68">
-        <v>-1255.353852538776</v>
+        <v>-1282.964254138776</v>
       </c>
       <c r="O68">
-        <v>-251.0707705077552</v>
+        <v>-256.5928508277552</v>
       </c>
       <c r="P68">
-        <v>-1004.283082031021</v>
+        <v>-1026.37140331102</v>
       </c>
       <c r="Q68">
-        <v>-244.5830820310207</v>
+        <v>-266.6714033110205</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1511686694912976</v>
+        <v>0.1543616594758824</v>
       </c>
       <c r="T68">
-        <v>2.05383149098678</v>
+        <v>2.11606880889547</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.0622221205413095</v>
+        <v>0.06129343217502131</v>
       </c>
       <c r="W68">
-        <v>0.1883057981953051</v>
+        <v>0.1884922788192557</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3111106027065474</v>
+        <v>0.3064671608751065</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1772291744359425</v>
+        <v>0.1787791744359426</v>
       </c>
       <c r="C69">
-        <v>-5046.444163839549</v>
+        <v>-5221.299901874987</v>
       </c>
       <c r="D69">
-        <v>3204.689836160451</v>
+        <v>3167.336098125013</v>
       </c>
       <c r="E69">
-        <v>621.8340000000007</v>
+        <v>759.3360000000011</v>
       </c>
       <c r="F69">
-        <v>9212.634</v>
+        <v>9350.136</v>
       </c>
       <c r="G69">
         <v>961.5</v>
@@ -6945,37 +6945,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M69">
-        <v>1849.8969072</v>
+        <v>1877.5073088</v>
       </c>
       <c r="N69">
-        <v>-1282.964254138776</v>
+        <v>-1310.574655738776</v>
       </c>
       <c r="O69">
-        <v>-256.5928508277552</v>
+        <v>-262.1149311477552</v>
       </c>
       <c r="P69">
-        <v>-1026.37140331102</v>
+        <v>-1048.45972459102</v>
       </c>
       <c r="Q69">
-        <v>-266.6714033110205</v>
+        <v>-288.7597245910205</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1543616594758824</v>
+        <v>0.1577542113345038</v>
       </c>
       <c r="T69">
-        <v>2.11606880889547</v>
+        <v>2.182195959173454</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06129343217502131</v>
+        <v>0.06039205817244746</v>
       </c>
       <c r="W69">
-        <v>0.1884922788192557</v>
+        <v>0.1886732747189726</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3064671608751065</v>
+        <v>0.3019602908622373</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1787791744359426</v>
+        <v>0.1803291744359425</v>
       </c>
       <c r="C70">
-        <v>-5221.299901874987</v>
+        <v>-5395.294885442885</v>
       </c>
       <c r="D70">
-        <v>3167.336098125013</v>
+        <v>3130.843114557115</v>
       </c>
       <c r="E70">
-        <v>759.3360000000011</v>
+        <v>896.8380000000016</v>
       </c>
       <c r="F70">
-        <v>9350.136</v>
+        <v>9487.638000000001</v>
       </c>
       <c r="G70">
         <v>961.5</v>
@@ -7027,37 +7027,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M70">
-        <v>1877.5073088</v>
+        <v>1905.1177104</v>
       </c>
       <c r="N70">
-        <v>-1310.574655738776</v>
+        <v>-1338.185057338776</v>
       </c>
       <c r="O70">
-        <v>-262.1149311477552</v>
+        <v>-267.6370114677552</v>
       </c>
       <c r="P70">
-        <v>-1048.45972459102</v>
+        <v>-1070.548045871021</v>
       </c>
       <c r="Q70">
-        <v>-288.7597245910205</v>
+        <v>-310.8480458710209</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1577542113345038</v>
+        <v>0.1613656375065845</v>
       </c>
       <c r="T70">
-        <v>2.182195959173454</v>
+        <v>2.252589377211307</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.06039205817244746</v>
+        <v>0.05951681095255691</v>
       </c>
       <c r="W70">
-        <v>0.1886732747189726</v>
+        <v>0.1888490243607266</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3019602908622373</v>
+        <v>0.2975840547627845</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1803291744359425</v>
+        <v>0.1818791744359425</v>
       </c>
       <c r="C71">
-        <v>-5395.294885442885</v>
+        <v>-5568.458527627874</v>
       </c>
       <c r="D71">
-        <v>3130.843114557115</v>
+        <v>3095.181472372126</v>
       </c>
       <c r="E71">
-        <v>896.8380000000016</v>
+        <v>1034.34</v>
       </c>
       <c r="F71">
-        <v>9487.638000000001</v>
+        <v>9625.139999999999</v>
       </c>
       <c r="G71">
         <v>961.5</v>
@@ -7109,37 +7109,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M71">
-        <v>1905.1177104</v>
+        <v>1932.728112</v>
       </c>
       <c r="N71">
-        <v>-1338.185057338776</v>
+        <v>-1365.795458938775</v>
       </c>
       <c r="O71">
-        <v>-267.6370114677552</v>
+        <v>-273.1590917877551</v>
       </c>
       <c r="P71">
-        <v>-1070.548045871021</v>
+        <v>-1092.63636715102</v>
       </c>
       <c r="Q71">
-        <v>-310.8480458710209</v>
+        <v>-332.9363671510204</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1613656375065845</v>
+        <v>0.1652178254234707</v>
       </c>
       <c r="T71">
-        <v>2.252589377211307</v>
+        <v>2.327675689785018</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05951681095255691</v>
+        <v>0.05866657079609183</v>
       </c>
       <c r="W71">
-        <v>0.1888490243607266</v>
+        <v>0.1890197525841448</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2975840547627845</v>
+        <v>0.2933328539804592</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1818791744359425</v>
+        <v>0.1834291744359426</v>
       </c>
       <c r="C72">
-        <v>-5568.458527627874</v>
+        <v>-5740.818916496652</v>
       </c>
       <c r="D72">
-        <v>3095.181472372126</v>
+        <v>3060.323083503347</v>
       </c>
       <c r="E72">
-        <v>1034.34</v>
+        <v>1171.842000000001</v>
       </c>
       <c r="F72">
-        <v>9625.139999999999</v>
+        <v>9762.642</v>
       </c>
       <c r="G72">
         <v>961.5</v>
@@ -7191,37 +7191,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M72">
-        <v>1932.728112</v>
+        <v>1960.3385136</v>
       </c>
       <c r="N72">
-        <v>-1365.795458938775</v>
+        <v>-1393.405860538775</v>
       </c>
       <c r="O72">
-        <v>-273.1590917877551</v>
+        <v>-278.6811721077551</v>
       </c>
       <c r="P72">
-        <v>-1092.63636715102</v>
+        <v>-1114.72468843102</v>
       </c>
       <c r="Q72">
-        <v>-332.9363671510204</v>
+        <v>-355.0246884310203</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1652178254234707</v>
+        <v>0.1693356814725559</v>
       </c>
       <c r="T72">
-        <v>2.327675689785018</v>
+        <v>2.407940368743123</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05866657079609183</v>
+        <v>0.0578402810665694</v>
       </c>
       <c r="W72">
-        <v>0.1890197525841448</v>
+        <v>0.1891856715618329</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2933328539804592</v>
+        <v>0.2892014053328471</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1834291744359425</v>
+        <v>0.1849791744359425</v>
       </c>
       <c r="C73">
-        <v>-5740.81891649665</v>
+        <v>-5912.402888879763</v>
       </c>
       <c r="D73">
-        <v>3060.323083503349</v>
+        <v>3026.241111120235</v>
       </c>
       <c r="E73">
-        <v>1171.841999999999</v>
+        <v>1309.343999999999</v>
       </c>
       <c r="F73">
-        <v>9762.641999999998</v>
+        <v>9900.143999999998</v>
       </c>
       <c r="G73">
         <v>961.5</v>
@@ -7273,37 +7273,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M73">
-        <v>1960.3385136</v>
+        <v>1987.9489152</v>
       </c>
       <c r="N73">
-        <v>-1393.405860538775</v>
+        <v>-1421.016262138775</v>
       </c>
       <c r="O73">
-        <v>-278.6811721077551</v>
+        <v>-284.2032524277551</v>
       </c>
       <c r="P73">
-        <v>-1114.72468843102</v>
+        <v>-1136.81300971102</v>
       </c>
       <c r="Q73">
-        <v>-355.0246884310203</v>
+        <v>-377.1130097110203</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1693356814725558</v>
+        <v>0.1737476700965757</v>
       </c>
       <c r="T73">
-        <v>2.407940368743121</v>
+        <v>2.493938239055375</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05784028106656941</v>
+        <v>0.05703694382953373</v>
       </c>
       <c r="W73">
-        <v>0.1891856715618329</v>
+        <v>0.1893469816790296</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.289201405332847</v>
+        <v>0.2851847191476685</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1849791744359425</v>
+        <v>0.1865291744359425</v>
       </c>
       <c r="C74">
-        <v>-5912.402888879763</v>
+        <v>-6083.236099277587</v>
       </c>
       <c r="D74">
-        <v>3026.241111120235</v>
+        <v>2992.909900722413</v>
       </c>
       <c r="E74">
-        <v>1309.343999999999</v>
+        <v>1446.846</v>
       </c>
       <c r="F74">
-        <v>9900.143999999998</v>
+        <v>10037.646</v>
       </c>
       <c r="G74">
         <v>961.5</v>
@@ -7355,37 +7355,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M74">
-        <v>1987.9489152</v>
+        <v>2015.5593168</v>
       </c>
       <c r="N74">
-        <v>-1421.016262138775</v>
+        <v>-1448.626663738775</v>
       </c>
       <c r="O74">
-        <v>-284.2032524277551</v>
+        <v>-289.7253327477551</v>
       </c>
       <c r="P74">
-        <v>-1136.81300971102</v>
+        <v>-1158.90133099102</v>
       </c>
       <c r="Q74">
-        <v>-377.1130097110203</v>
+        <v>-399.2013309910202</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1737476700965757</v>
+        <v>0.1784864726927452</v>
       </c>
       <c r="T74">
-        <v>2.493938239055375</v>
+        <v>2.586306321983352</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05703694382953373</v>
+        <v>0.05625561583186888</v>
       </c>
       <c r="W74">
-        <v>0.1893469816790296</v>
+        <v>0.1895038723409607</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2851847191476685</v>
+        <v>0.2812780791593444</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1865291744359425</v>
+        <v>0.1880791744359425</v>
       </c>
       <c r="C75">
-        <v>-6083.236099277587</v>
+        <v>-6253.343084262289</v>
       </c>
       <c r="D75">
-        <v>2992.909900722413</v>
+        <v>2960.30491573771</v>
       </c>
       <c r="E75">
-        <v>1446.846</v>
+        <v>1584.348</v>
       </c>
       <c r="F75">
-        <v>10037.646</v>
+        <v>10175.148</v>
       </c>
       <c r="G75">
         <v>961.5</v>
@@ -7437,37 +7437,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M75">
-        <v>2015.5593168</v>
+        <v>2043.1697184</v>
       </c>
       <c r="N75">
-        <v>-1448.626663738775</v>
+        <v>-1476.237065338776</v>
       </c>
       <c r="O75">
-        <v>-289.7253327477551</v>
+        <v>-295.2474130677551</v>
       </c>
       <c r="P75">
-        <v>-1158.90133099102</v>
+        <v>-1180.989652271021</v>
       </c>
       <c r="Q75">
-        <v>-399.2013309910202</v>
+        <v>-421.2896522710206</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1784864726927452</v>
+        <v>0.1835897985655431</v>
       </c>
       <c r="T75">
-        <v>2.586306321983352</v>
+        <v>2.685779642059635</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05625561583186888</v>
+        <v>0.05549540480711389</v>
       </c>
       <c r="W75">
-        <v>0.1895038723409607</v>
+        <v>0.1896565227147315</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2812780791593444</v>
+        <v>0.2774770240355694</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1880791744359425</v>
+        <v>0.1896291744359425</v>
       </c>
       <c r="C76">
-        <v>-6253.343084262289</v>
+        <v>-6422.747322715566</v>
       </c>
       <c r="D76">
-        <v>2960.30491573771</v>
+        <v>2928.402677284434</v>
       </c>
       <c r="E76">
-        <v>1584.348</v>
+        <v>1721.85</v>
       </c>
       <c r="F76">
-        <v>10175.148</v>
+        <v>10312.65</v>
       </c>
       <c r="G76">
         <v>961.5</v>
@@ -7519,37 +7519,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M76">
-        <v>2043.1697184</v>
+        <v>2070.78012</v>
       </c>
       <c r="N76">
-        <v>-1476.237065338776</v>
+        <v>-1503.847466938776</v>
       </c>
       <c r="O76">
-        <v>-295.2474130677551</v>
+        <v>-300.7694933877551</v>
       </c>
       <c r="P76">
-        <v>-1180.989652271021</v>
+        <v>-1203.07797355102</v>
       </c>
       <c r="Q76">
-        <v>-421.2896522710206</v>
+        <v>-443.3779735510205</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1835897985655431</v>
+        <v>0.1891013905081648</v>
       </c>
       <c r="T76">
-        <v>2.685779642059635</v>
+        <v>2.793210827742021</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05549540480711389</v>
+        <v>0.05475546607635237</v>
       </c>
       <c r="W76">
-        <v>0.1896565227147315</v>
+        <v>0.1898051024118684</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2774770240355694</v>
+        <v>0.2737773303817618</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1896291744359425</v>
+        <v>0.1911791744359425</v>
       </c>
       <c r="C77">
-        <v>-6422.747322715566</v>
+        <v>-6591.47129221293</v>
       </c>
       <c r="D77">
-        <v>2928.402677284434</v>
+        <v>2897.18070778707</v>
       </c>
       <c r="E77">
-        <v>1721.85</v>
+        <v>1859.352000000001</v>
       </c>
       <c r="F77">
-        <v>10312.65</v>
+        <v>10450.152</v>
       </c>
       <c r="G77">
         <v>961.5</v>
@@ -7601,37 +7601,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M77">
-        <v>2070.78012</v>
+        <v>2098.3905216</v>
       </c>
       <c r="N77">
-        <v>-1503.847466938776</v>
+        <v>-1531.457868538776</v>
       </c>
       <c r="O77">
-        <v>-300.7694933877551</v>
+        <v>-306.2915737077552</v>
       </c>
       <c r="P77">
-        <v>-1203.07797355102</v>
+        <v>-1225.166294831021</v>
       </c>
       <c r="Q77">
-        <v>-443.3779735510205</v>
+        <v>-465.4662948310209</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1891013905081648</v>
+        <v>0.1950722817793384</v>
       </c>
       <c r="T77">
-        <v>2.793210827742021</v>
+        <v>2.909594612231272</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05475546607635237</v>
+        <v>0.05403499941745299</v>
       </c>
       <c r="W77">
-        <v>0.1898051024118684</v>
+        <v>0.1899497721169754</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2737773303817618</v>
+        <v>0.2701749970872649</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1911791744359425</v>
+        <v>0.1927291744359425</v>
       </c>
       <c r="C78">
-        <v>-6591.47129221293</v>
+        <v>-6759.536521839103</v>
       </c>
       <c r="D78">
-        <v>2897.18070778707</v>
+        <v>2866.617478160895</v>
       </c>
       <c r="E78">
-        <v>1859.352000000001</v>
+        <v>1996.853999999999</v>
       </c>
       <c r="F78">
-        <v>10450.152</v>
+        <v>10587.654</v>
       </c>
       <c r="G78">
         <v>961.5</v>
@@ -7683,37 +7683,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M78">
-        <v>2098.3905216</v>
+        <v>2126.0009232</v>
       </c>
       <c r="N78">
-        <v>-1531.457868538776</v>
+        <v>-1559.068270138775</v>
       </c>
       <c r="O78">
-        <v>-306.2915737077552</v>
+        <v>-311.8136540277551</v>
       </c>
       <c r="P78">
-        <v>-1225.166294831021</v>
+        <v>-1247.25461611102</v>
       </c>
       <c r="Q78">
-        <v>-465.4662948310209</v>
+        <v>-487.5546161110204</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1950722817793384</v>
+        <v>0.2015623809871357</v>
       </c>
       <c r="T78">
-        <v>2.909594612231272</v>
+        <v>3.036098725806545</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05403499941745299</v>
+        <v>0.05333324617826531</v>
       </c>
       <c r="W78">
-        <v>0.1899497721169754</v>
+        <v>0.1900906841674043</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2701749970872649</v>
+        <v>0.2666662308913265</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1927291744359425</v>
+        <v>0.1942791744359426</v>
       </c>
       <c r="C79">
-        <v>-6759.536521839103</v>
+        <v>-6926.963641695333</v>
       </c>
       <c r="D79">
-        <v>2866.617478160895</v>
+        <v>2836.692358304667</v>
       </c>
       <c r="E79">
-        <v>1996.853999999999</v>
+        <v>2134.356</v>
       </c>
       <c r="F79">
-        <v>10587.654</v>
+        <v>10725.156</v>
       </c>
       <c r="G79">
         <v>961.5</v>
@@ -7765,37 +7765,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M79">
-        <v>2126.0009232</v>
+        <v>2153.6113248</v>
       </c>
       <c r="N79">
-        <v>-1559.068270138775</v>
+        <v>-1586.678671738775</v>
       </c>
       <c r="O79">
-        <v>-311.8136540277551</v>
+        <v>-317.3357343477551</v>
       </c>
       <c r="P79">
-        <v>-1247.25461611102</v>
+        <v>-1269.34293739102</v>
       </c>
       <c r="Q79">
-        <v>-487.5546161110204</v>
+        <v>-509.6429373910204</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2015623809871357</v>
+        <v>0.2086424892138236</v>
       </c>
       <c r="T79">
-        <v>3.036098725806545</v>
+        <v>3.174103213343206</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.05333324617826531</v>
+        <v>0.05264948661187729</v>
       </c>
       <c r="W79">
-        <v>0.1900906841674043</v>
+        <v>0.1902279830883351</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2666662308913265</v>
+        <v>0.2632474330593864</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1942791744359426</v>
+        <v>0.1958291744359426</v>
       </c>
       <c r="C80">
-        <v>-6926.963641695333</v>
+        <v>-7093.772429337822</v>
       </c>
       <c r="D80">
-        <v>2836.692358304667</v>
+        <v>2807.385570662177</v>
       </c>
       <c r="E80">
-        <v>2134.356</v>
+        <v>2271.858</v>
       </c>
       <c r="F80">
-        <v>10725.156</v>
+        <v>10862.658</v>
       </c>
       <c r="G80">
         <v>961.5</v>
@@ -7847,37 +7847,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M80">
-        <v>2153.6113248</v>
+        <v>2181.2217264</v>
       </c>
       <c r="N80">
-        <v>-1586.678671738775</v>
+        <v>-1614.289073338776</v>
       </c>
       <c r="O80">
-        <v>-317.3357343477551</v>
+        <v>-322.8578146677552</v>
       </c>
       <c r="P80">
-        <v>-1269.34293739102</v>
+        <v>-1291.431258671021</v>
       </c>
       <c r="Q80">
-        <v>-509.6429373910204</v>
+        <v>-531.7312586710208</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2086424892138236</v>
+        <v>0.216396893462101</v>
       </c>
       <c r="T80">
-        <v>3.174103213343206</v>
+        <v>3.325250985407168</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05264948661187729</v>
+        <v>0.05198303741425857</v>
       </c>
       <c r="W80">
-        <v>0.1902279830883351</v>
+        <v>0.1903618060872169</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2632474330593864</v>
+        <v>0.2599151870712928</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1958291744359426</v>
+        <v>0.1973791744359426</v>
       </c>
       <c r="C81">
-        <v>-7093.772429337822</v>
+        <v>-7259.981853367008</v>
       </c>
       <c r="D81">
-        <v>2807.385570662177</v>
+        <v>2778.678146632993</v>
       </c>
       <c r="E81">
-        <v>2271.858</v>
+        <v>2409.360000000001</v>
       </c>
       <c r="F81">
-        <v>10862.658</v>
+        <v>11000.16</v>
       </c>
       <c r="G81">
         <v>961.5</v>
@@ -7929,37 +7929,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M81">
-        <v>2181.2217264</v>
+        <v>2208.832128</v>
       </c>
       <c r="N81">
-        <v>-1614.289073338776</v>
+        <v>-1641.899474938776</v>
       </c>
       <c r="O81">
-        <v>-322.8578146677552</v>
+        <v>-328.3798949877552</v>
       </c>
       <c r="P81">
-        <v>-1291.431258671021</v>
+        <v>-1313.519579951021</v>
       </c>
       <c r="Q81">
-        <v>-531.7312586710208</v>
+        <v>-553.8195799510207</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.216396893462101</v>
+        <v>0.224926738135206</v>
       </c>
       <c r="T81">
-        <v>3.325250985407168</v>
+        <v>3.491513534677527</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05198303741425857</v>
+        <v>0.05133324944658035</v>
       </c>
       <c r="W81">
-        <v>0.1903618060872169</v>
+        <v>0.1904922835111267</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2599151870712928</v>
+        <v>0.2566662472329017</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1973791744359426</v>
+        <v>0.1989291744359425</v>
       </c>
       <c r="C82">
-        <v>-7259.981853367008</v>
+        <v>-7425.610114369498</v>
       </c>
       <c r="D82">
-        <v>2778.678146632993</v>
+        <v>2750.551885630503</v>
       </c>
       <c r="E82">
-        <v>2409.360000000001</v>
+        <v>2546.862000000001</v>
       </c>
       <c r="F82">
-        <v>11000.16</v>
+        <v>11137.662</v>
       </c>
       <c r="G82">
         <v>961.5</v>
@@ -8011,37 +8011,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M82">
-        <v>2208.832128</v>
+        <v>2236.4425296</v>
       </c>
       <c r="N82">
-        <v>-1641.899474938776</v>
+        <v>-1669.509876538776</v>
       </c>
       <c r="O82">
-        <v>-328.3798949877552</v>
+        <v>-333.9019753077552</v>
       </c>
       <c r="P82">
-        <v>-1313.519579951021</v>
+        <v>-1335.607901231021</v>
       </c>
       <c r="Q82">
-        <v>-553.8195799510207</v>
+        <v>-575.9079012310207</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.224926738135206</v>
+        <v>0.2343544611949537</v>
       </c>
       <c r="T82">
-        <v>3.491513534677527</v>
+        <v>3.675277404923712</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.05133324944658035</v>
+        <v>0.05069950562625219</v>
       </c>
       <c r="W82">
-        <v>0.1904922835111267</v>
+        <v>0.1906195392702486</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2566662472329017</v>
+        <v>0.2534975281312609</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1989291744359425</v>
+        <v>0.2004791744359425</v>
       </c>
       <c r="C83">
-        <v>-7425.610114369498</v>
+        <v>-7590.674683398421</v>
       </c>
       <c r="D83">
-        <v>2750.551885630503</v>
+        <v>2722.98931660158</v>
       </c>
       <c r="E83">
-        <v>2546.862000000001</v>
+        <v>2684.364000000001</v>
       </c>
       <c r="F83">
-        <v>11137.662</v>
+        <v>11275.164</v>
       </c>
       <c r="G83">
         <v>961.5</v>
@@ -8093,37 +8093,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M83">
-        <v>2236.4425296</v>
+        <v>2264.0529312</v>
       </c>
       <c r="N83">
-        <v>-1669.509876538776</v>
+        <v>-1697.120278138776</v>
       </c>
       <c r="O83">
-        <v>-333.9019753077552</v>
+        <v>-339.4240556277553</v>
       </c>
       <c r="P83">
-        <v>-1335.607901231021</v>
+        <v>-1357.696222511021</v>
       </c>
       <c r="Q83">
-        <v>-575.9079012310207</v>
+        <v>-597.9962225110208</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2343544611949537</v>
+        <v>0.2448297090391178</v>
       </c>
       <c r="T83">
-        <v>3.675277404923712</v>
+        <v>3.87945948297503</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.05069950562625219</v>
+        <v>0.0500812189722735</v>
       </c>
       <c r="W83">
-        <v>0.1906195392702486</v>
+        <v>0.1907436912303675</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2534975281312609</v>
+        <v>0.2504060948613674</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2004791744359425</v>
+        <v>0.2020291744359425</v>
       </c>
       <c r="C84">
-        <v>-7590.674683398421</v>
+        <v>-7755.1923381631</v>
       </c>
       <c r="D84">
-        <v>2722.98931660158</v>
+        <v>2695.9736618369</v>
       </c>
       <c r="E84">
-        <v>2684.364000000001</v>
+        <v>2821.866</v>
       </c>
       <c r="F84">
-        <v>11275.164</v>
+        <v>11412.666</v>
       </c>
       <c r="G84">
         <v>961.5</v>
@@ -8175,37 +8175,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M84">
-        <v>2264.0529312</v>
+        <v>2291.6633328</v>
       </c>
       <c r="N84">
-        <v>-1697.120278138776</v>
+        <v>-1724.730679738776</v>
       </c>
       <c r="O84">
-        <v>-339.4240556277553</v>
+        <v>-344.9461359477551</v>
       </c>
       <c r="P84">
-        <v>-1357.696222511021</v>
+        <v>-1379.78454379102</v>
       </c>
       <c r="Q84">
-        <v>-597.9962225110208</v>
+        <v>-620.0845437910206</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2448297090391178</v>
+        <v>0.2565373389825953</v>
       </c>
       <c r="T84">
-        <v>3.87945948297503</v>
+        <v>4.107662981973562</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.0500812189722735</v>
+        <v>0.04947783079188468</v>
       </c>
       <c r="W84">
-        <v>0.1907436912303675</v>
+        <v>0.1908648515769895</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2504060948613674</v>
+        <v>0.2473891539594233</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2020291744359425</v>
+        <v>0.2035791744359425</v>
       </c>
       <c r="C85">
-        <v>-7755.1923381631</v>
+        <v>-7919.179197085617</v>
       </c>
       <c r="D85">
-        <v>2695.9736618369</v>
+        <v>2669.488802914382</v>
       </c>
       <c r="E85">
-        <v>2821.866</v>
+        <v>2959.368</v>
       </c>
       <c r="F85">
-        <v>11412.666</v>
+        <v>11550.168</v>
       </c>
       <c r="G85">
         <v>961.5</v>
@@ -8257,37 +8257,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M85">
-        <v>2291.6633328</v>
+        <v>2319.2737344</v>
       </c>
       <c r="N85">
-        <v>-1724.730679738776</v>
+        <v>-1752.341081338776</v>
       </c>
       <c r="O85">
-        <v>-344.9461359477551</v>
+        <v>-350.4682162677552</v>
       </c>
       <c r="P85">
-        <v>-1379.78454379102</v>
+        <v>-1401.872865071021</v>
       </c>
       <c r="Q85">
-        <v>-620.0845437910206</v>
+        <v>-642.1728650710207</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2565373389825953</v>
+        <v>0.2697084226690076</v>
       </c>
       <c r="T85">
-        <v>4.107662981973562</v>
+        <v>4.36439191834691</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.04947783079188468</v>
+        <v>0.04888880899674319</v>
       </c>
       <c r="W85">
-        <v>0.1908648515769895</v>
+        <v>0.190983127153454</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2473891539594233</v>
+        <v>0.2444440449837159</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2035791744359425</v>
+        <v>0.2051291744359425</v>
       </c>
       <c r="C86">
-        <v>-7919.179197085616</v>
+        <v>-8082.650751369478</v>
       </c>
       <c r="D86">
-        <v>2669.488802914382</v>
+        <v>2643.51924863052</v>
       </c>
       <c r="E86">
-        <v>2959.367999999999</v>
+        <v>3096.869999999999</v>
       </c>
       <c r="F86">
-        <v>11550.168</v>
+        <v>11687.67</v>
       </c>
       <c r="G86">
         <v>961.5</v>
@@ -8339,37 +8339,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M86">
-        <v>2319.2737344</v>
+        <v>2346.884136</v>
       </c>
       <c r="N86">
-        <v>-1752.341081338775</v>
+        <v>-1779.951482938775</v>
       </c>
       <c r="O86">
-        <v>-350.4682162677551</v>
+        <v>-355.9902965877551</v>
       </c>
       <c r="P86">
-        <v>-1401.87286507102</v>
+        <v>-1423.96118635102</v>
       </c>
       <c r="Q86">
-        <v>-642.1728650710205</v>
+        <v>-664.2611863510205</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2697084226690075</v>
+        <v>0.2846356508469413</v>
       </c>
       <c r="T86">
-        <v>4.364391918346907</v>
+        <v>4.655351379570035</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.04888880899674319</v>
+        <v>0.04831364653795798</v>
       </c>
       <c r="W86">
-        <v>0.190983127153454</v>
+        <v>0.191098619775178</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2444440449837159</v>
+        <v>0.2415682326897899</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2051291744359425</v>
+        <v>0.2066791744359425</v>
       </c>
       <c r="C87">
-        <v>-8082.650751369478</v>
+        <v>-8245.621895214499</v>
       </c>
       <c r="D87">
-        <v>2643.51924863052</v>
+        <v>2618.0501047855</v>
       </c>
       <c r="E87">
-        <v>3096.869999999999</v>
+        <v>3234.371999999999</v>
       </c>
       <c r="F87">
-        <v>11687.67</v>
+        <v>11825.172</v>
       </c>
       <c r="G87">
         <v>961.5</v>
@@ -8421,37 +8421,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M87">
-        <v>2346.884136</v>
+        <v>2374.4945376</v>
       </c>
       <c r="N87">
-        <v>-1779.951482938775</v>
+        <v>-1807.561884538775</v>
       </c>
       <c r="O87">
-        <v>-355.9902965877551</v>
+        <v>-361.5123769077551</v>
       </c>
       <c r="P87">
-        <v>-1423.96118635102</v>
+        <v>-1446.04950763102</v>
       </c>
       <c r="Q87">
-        <v>-664.2611863510205</v>
+        <v>-686.3495076310204</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2846356508469413</v>
+        <v>0.3016953401931514</v>
       </c>
       <c r="T87">
-        <v>4.655351379570035</v>
+        <v>4.987876478110751</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.04831364653795798</v>
+        <v>0.04775185995030731</v>
       </c>
       <c r="W87">
-        <v>0.191098619775178</v>
+        <v>0.1912114265219783</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2415682326897899</v>
+        <v>0.2387592997515364</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2066791744359425</v>
+        <v>0.2082291744359425</v>
       </c>
       <c r="C88">
-        <v>-8245.621895214499</v>
+        <v>-8408.106954301697</v>
       </c>
       <c r="D88">
-        <v>2618.0501047855</v>
+        <v>2593.067045698303</v>
       </c>
       <c r="E88">
-        <v>3234.371999999999</v>
+        <v>3371.874</v>
       </c>
       <c r="F88">
-        <v>11825.172</v>
+        <v>11962.674</v>
       </c>
       <c r="G88">
         <v>961.5</v>
@@ -8503,37 +8503,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M88">
-        <v>2374.4945376</v>
+        <v>2402.1049392</v>
       </c>
       <c r="N88">
-        <v>-1807.561884538775</v>
+        <v>-1835.172286138776</v>
       </c>
       <c r="O88">
-        <v>-361.5123769077551</v>
+        <v>-367.0344572277552</v>
       </c>
       <c r="P88">
-        <v>-1446.04950763102</v>
+        <v>-1468.137828911021</v>
       </c>
       <c r="Q88">
-        <v>-686.3495076310204</v>
+        <v>-708.4378289110206</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3016953401931514</v>
+        <v>0.3213795971310861</v>
       </c>
       <c r="T88">
-        <v>4.987876478110751</v>
+        <v>5.37155928411927</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.04775185995030731</v>
+        <v>0.04720298799685549</v>
       </c>
       <c r="W88">
-        <v>0.1912114265219783</v>
+        <v>0.1913216400102314</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2387592997515364</v>
+        <v>0.2360149399842774</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2082291744359425</v>
+        <v>0.2097791744359426</v>
       </c>
       <c r="C89">
-        <v>-8408.106954301697</v>
+        <v>-8570.119712662676</v>
       </c>
       <c r="D89">
-        <v>2593.067045698303</v>
+        <v>2568.556287337323</v>
       </c>
       <c r="E89">
-        <v>3371.874</v>
+        <v>3509.376</v>
       </c>
       <c r="F89">
-        <v>11962.674</v>
+        <v>12100.176</v>
       </c>
       <c r="G89">
         <v>961.5</v>
@@ -8585,37 +8585,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M89">
-        <v>2402.1049392</v>
+        <v>2429.7153408</v>
       </c>
       <c r="N89">
-        <v>-1835.172286138776</v>
+        <v>-1862.782687738776</v>
       </c>
       <c r="O89">
-        <v>-367.0344572277552</v>
+        <v>-372.5565375477552</v>
       </c>
       <c r="P89">
-        <v>-1468.137828911021</v>
+        <v>-1490.22615019102</v>
       </c>
       <c r="Q89">
-        <v>-708.4378289110206</v>
+        <v>-730.5261501910205</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3213795971310861</v>
+        <v>0.3443445635586767</v>
       </c>
       <c r="T89">
-        <v>5.37155928411927</v>
+        <v>5.819189224462544</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.04720298799685549</v>
+        <v>0.04666659040598214</v>
       </c>
       <c r="W89">
-        <v>0.1913216400102314</v>
+        <v>0.1914293486464788</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2360149399842774</v>
+        <v>0.2333329520299107</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2097791744359426</v>
+        <v>0.2113291744359425</v>
       </c>
       <c r="C90">
-        <v>-8570.119712662676</v>
+        <v>-8731.673438039423</v>
       </c>
       <c r="D90">
-        <v>2568.556287337323</v>
+        <v>2544.504561960577</v>
       </c>
       <c r="E90">
-        <v>3509.376</v>
+        <v>3646.878000000001</v>
       </c>
       <c r="F90">
-        <v>12100.176</v>
+        <v>12237.678</v>
       </c>
       <c r="G90">
         <v>961.5</v>
@@ -8667,37 +8667,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M90">
-        <v>2429.7153408</v>
+        <v>2457.3257424</v>
       </c>
       <c r="N90">
-        <v>-1862.782687738776</v>
+        <v>-1890.393089338776</v>
       </c>
       <c r="O90">
-        <v>-372.5565375477552</v>
+        <v>-378.0786178677552</v>
       </c>
       <c r="P90">
-        <v>-1490.22615019102</v>
+        <v>-1512.31447147102</v>
       </c>
       <c r="Q90">
-        <v>-730.5261501910205</v>
+        <v>-752.6144714710205</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3443445635586767</v>
+        <v>0.3714849784276473</v>
       </c>
       <c r="T90">
-        <v>5.819189224462544</v>
+        <v>6.348206426686412</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.04666659040598214</v>
+        <v>0.04614224669355537</v>
       </c>
       <c r="W90">
-        <v>0.1914293486464788</v>
+        <v>0.1915346368639341</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2333329520299107</v>
+        <v>0.2307112334677768</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2113291744359425</v>
+        <v>0.2128791744359425</v>
       </c>
       <c r="C91">
-        <v>-8731.673438039423</v>
+        <v>-8892.780905832482</v>
       </c>
       <c r="D91">
-        <v>2544.504561960577</v>
+        <v>2520.899094167516</v>
       </c>
       <c r="E91">
-        <v>3646.878000000001</v>
+        <v>3784.379999999999</v>
       </c>
       <c r="F91">
-        <v>12237.678</v>
+        <v>12375.18</v>
       </c>
       <c r="G91">
         <v>961.5</v>
@@ -8749,37 +8749,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M91">
-        <v>2457.3257424</v>
+        <v>2484.936144</v>
       </c>
       <c r="N91">
-        <v>-1890.393089338776</v>
+        <v>-1918.003490938775</v>
       </c>
       <c r="O91">
-        <v>-378.0786178677552</v>
+        <v>-383.6006981877551</v>
       </c>
       <c r="P91">
-        <v>-1512.31447147102</v>
+        <v>-1534.40279275102</v>
       </c>
       <c r="Q91">
-        <v>-752.6144714710205</v>
+        <v>-774.7027927510204</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3714849784276473</v>
+        <v>0.404053476270412</v>
       </c>
       <c r="T91">
-        <v>6.348206426686412</v>
+        <v>6.983027069355053</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.04614224669355537</v>
+        <v>0.04562955506362698</v>
       </c>
       <c r="W91">
-        <v>0.1915346368639341</v>
+        <v>0.1916375853432237</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2307112334677768</v>
+        <v>0.2281477753181348</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2128791744359425</v>
+        <v>0.2144291744359425</v>
       </c>
       <c r="C92">
-        <v>-8892.780905832482</v>
+        <v>-9053.454421728411</v>
       </c>
       <c r="D92">
-        <v>2520.899094167516</v>
+        <v>2497.727578271587</v>
       </c>
       <c r="E92">
-        <v>3784.379999999999</v>
+        <v>3921.882</v>
       </c>
       <c r="F92">
-        <v>12375.18</v>
+        <v>12512.682</v>
       </c>
       <c r="G92">
         <v>961.5</v>
@@ -8831,37 +8831,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M92">
-        <v>2484.936144</v>
+        <v>2512.5465456</v>
       </c>
       <c r="N92">
-        <v>-1918.003490938775</v>
+        <v>-1945.613892538775</v>
       </c>
       <c r="O92">
-        <v>-383.6006981877551</v>
+        <v>-389.1227785077551</v>
       </c>
       <c r="P92">
-        <v>-1534.40279275102</v>
+        <v>-1556.49111403102</v>
       </c>
       <c r="Q92">
-        <v>-774.7027927510204</v>
+        <v>-796.7911140310204</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.404053476270412</v>
+        <v>0.4438594180782356</v>
       </c>
       <c r="T92">
-        <v>6.983027069355053</v>
+        <v>7.75891896595006</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.04562955506362698</v>
+        <v>0.0451281313816091</v>
       </c>
       <c r="W92">
-        <v>0.1916375853432237</v>
+        <v>0.1917382712185729</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2281477753181348</v>
+        <v>0.2256406569080455</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2144291744359425</v>
+        <v>0.2159791744359426</v>
       </c>
       <c r="C93">
-        <v>-9053.454421728411</v>
+        <v>-9213.705843090649</v>
       </c>
       <c r="D93">
-        <v>2497.727578271587</v>
+        <v>2474.97815690935</v>
       </c>
       <c r="E93">
-        <v>3921.882</v>
+        <v>4059.384</v>
       </c>
       <c r="F93">
-        <v>12512.682</v>
+        <v>12650.184</v>
       </c>
       <c r="G93">
         <v>961.5</v>
@@ -8913,37 +8913,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M93">
-        <v>2512.5465456</v>
+        <v>2540.1569472</v>
       </c>
       <c r="N93">
-        <v>-1945.613892538775</v>
+        <v>-1973.224294138776</v>
       </c>
       <c r="O93">
-        <v>-389.1227785077551</v>
+        <v>-394.6448588277552</v>
       </c>
       <c r="P93">
-        <v>-1556.49111403102</v>
+        <v>-1578.579435311021</v>
       </c>
       <c r="Q93">
-        <v>-796.7911140310204</v>
+        <v>-818.8794353110208</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4438594180782356</v>
+        <v>0.4936168453380152</v>
       </c>
       <c r="T93">
-        <v>7.75891896595006</v>
+        <v>8.72878383669382</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0451281313816091</v>
+        <v>0.04463760821441769</v>
       </c>
       <c r="W93">
-        <v>0.1917382712185729</v>
+        <v>0.1918367682705449</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2256406569080455</v>
+        <v>0.2231880410720885</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2159791744359426</v>
+        <v>0.2175291744359425</v>
       </c>
       <c r="C94">
-        <v>-9213.705843090649</v>
+        <v>-9373.546599191992</v>
       </c>
       <c r="D94">
-        <v>2474.97815690935</v>
+        <v>2452.639400808008</v>
       </c>
       <c r="E94">
-        <v>4059.384</v>
+        <v>4196.886</v>
       </c>
       <c r="F94">
-        <v>12650.184</v>
+        <v>12787.686</v>
       </c>
       <c r="G94">
         <v>961.5</v>
@@ -8995,37 +8995,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M94">
-        <v>2540.1569472</v>
+        <v>2567.7673488</v>
       </c>
       <c r="N94">
-        <v>-1973.224294138776</v>
+        <v>-2000.834695738776</v>
       </c>
       <c r="O94">
-        <v>-394.6448588277552</v>
+        <v>-400.1669391477552</v>
       </c>
       <c r="P94">
-        <v>-1578.579435311021</v>
+        <v>-1600.667756591021</v>
       </c>
       <c r="Q94">
-        <v>-818.8794353110208</v>
+        <v>-840.9677565910207</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4936168453380152</v>
+        <v>0.5575906803863031</v>
       </c>
       <c r="T94">
-        <v>8.72878383669382</v>
+        <v>9.975752956221511</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.04463760821441769</v>
+        <v>0.04415763393254223</v>
       </c>
       <c r="W94">
-        <v>0.1918367682705449</v>
+        <v>0.1919331471063455</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2231880410720885</v>
+        <v>0.2207881696627111</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2175291744359425</v>
+        <v>0.2190791744359425</v>
       </c>
       <c r="C95">
-        <v>-9373.546599191992</v>
+        <v>-9532.987710361165</v>
       </c>
       <c r="D95">
-        <v>2452.639400808008</v>
+        <v>2430.700289638835</v>
       </c>
       <c r="E95">
-        <v>4196.886</v>
+        <v>4334.388000000001</v>
       </c>
       <c r="F95">
-        <v>12787.686</v>
+        <v>12925.188</v>
       </c>
       <c r="G95">
         <v>961.5</v>
@@ -9077,37 +9077,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M95">
-        <v>2567.7673488</v>
+        <v>2595.3777504</v>
       </c>
       <c r="N95">
-        <v>-2000.834695738776</v>
+        <v>-2028.445097338776</v>
       </c>
       <c r="O95">
-        <v>-400.1669391477552</v>
+        <v>-405.6890194677551</v>
       </c>
       <c r="P95">
-        <v>-1600.667756591021</v>
+        <v>-1622.756077871021</v>
       </c>
       <c r="Q95">
-        <v>-840.9677565910207</v>
+        <v>-863.0560778710206</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5575906803863031</v>
+        <v>0.6428891271173538</v>
       </c>
       <c r="T95">
-        <v>9.975752956221511</v>
+        <v>11.6383784489251</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.04415763393254223</v>
+        <v>0.04368787186943008</v>
       </c>
       <c r="W95">
-        <v>0.1919331471063455</v>
+        <v>0.1920274753286184</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2207881696627111</v>
+        <v>0.2184393593471503</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2190791744359425</v>
+        <v>0.2206291744359425</v>
       </c>
       <c r="C96">
-        <v>-9532.987710361165</v>
+        <v>-9692.039806110892</v>
       </c>
       <c r="D96">
-        <v>2430.700289638835</v>
+        <v>2409.150193889109</v>
       </c>
       <c r="E96">
-        <v>4334.388000000001</v>
+        <v>4471.890000000001</v>
       </c>
       <c r="F96">
-        <v>12925.188</v>
+        <v>13062.69</v>
       </c>
       <c r="G96">
         <v>961.5</v>
@@ -9159,37 +9159,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M96">
-        <v>2595.3777504</v>
+        <v>2622.988152</v>
       </c>
       <c r="N96">
-        <v>-2028.445097338776</v>
+        <v>-2056.055498938776</v>
       </c>
       <c r="O96">
-        <v>-405.6890194677551</v>
+        <v>-411.2110997877552</v>
       </c>
       <c r="P96">
-        <v>-1622.756077871021</v>
+        <v>-1644.844399151021</v>
       </c>
       <c r="Q96">
-        <v>-863.0560778710206</v>
+        <v>-885.1443991510208</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6428891271173538</v>
+        <v>0.762306952540825</v>
       </c>
       <c r="T96">
-        <v>11.6383784489251</v>
+        <v>13.96605413871013</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.04368787186943008</v>
+        <v>0.04322799953396239</v>
       </c>
       <c r="W96">
-        <v>0.1920274753286184</v>
+        <v>0.1921198176935804</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2184393593471503</v>
+        <v>0.216139997669812</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2206291744359425</v>
+        <v>0.2221791744359425</v>
       </c>
       <c r="C97">
-        <v>-9692.039806110892</v>
+        <v>-9850.713142310131</v>
       </c>
       <c r="D97">
-        <v>2409.150193889109</v>
+        <v>2387.978857689868</v>
       </c>
       <c r="E97">
-        <v>4471.890000000001</v>
+        <v>4609.392</v>
       </c>
       <c r="F97">
-        <v>13062.69</v>
+        <v>13200.192</v>
       </c>
       <c r="G97">
         <v>961.5</v>
@@ -9241,37 +9241,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M97">
-        <v>2622.988152</v>
+        <v>2650.5985536</v>
       </c>
       <c r="N97">
-        <v>-2056.055498938776</v>
+        <v>-2083.665900538776</v>
       </c>
       <c r="O97">
-        <v>-411.2110997877552</v>
+        <v>-416.7331801077551</v>
       </c>
       <c r="P97">
-        <v>-1644.844399151021</v>
+        <v>-1666.93272043102</v>
       </c>
       <c r="Q97">
-        <v>-885.1443991510208</v>
+        <v>-907.2327204310205</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.762306952540825</v>
+        <v>0.9414336906760314</v>
       </c>
       <c r="T97">
-        <v>13.96605413871013</v>
+        <v>17.45756767338766</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.04322799953396239</v>
+        <v>0.04277770787215029</v>
       </c>
       <c r="W97">
-        <v>0.1921198176935804</v>
+        <v>0.1922102362592722</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.216139997669812</v>
+        <v>0.2138885393607514</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2221791744359425</v>
+        <v>0.2237291744359425</v>
       </c>
       <c r="C98">
-        <v>-9850.713142310131</v>
+        <v>-10009.01761745876</v>
       </c>
       <c r="D98">
-        <v>2387.978857689868</v>
+        <v>2367.17638254124</v>
       </c>
       <c r="E98">
-        <v>4609.392</v>
+        <v>4746.893999999998</v>
       </c>
       <c r="F98">
-        <v>13200.192</v>
+        <v>13337.694</v>
       </c>
       <c r="G98">
         <v>961.5</v>
@@ -9323,37 +9323,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M98">
-        <v>2650.5985536</v>
+        <v>2678.2089552</v>
       </c>
       <c r="N98">
-        <v>-2083.665900538776</v>
+        <v>-2111.276302138775</v>
       </c>
       <c r="O98">
-        <v>-416.7331801077551</v>
+        <v>-422.2552604277551</v>
       </c>
       <c r="P98">
-        <v>-1666.93272043102</v>
+        <v>-1689.02104171102</v>
       </c>
       <c r="Q98">
-        <v>-907.2327204310205</v>
+        <v>-929.3210417110205</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9414336906760291</v>
+        <v>1.239978254234706</v>
       </c>
       <c r="T98">
-        <v>17.45756767338762</v>
+        <v>23.27675689785016</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.04277770787215029</v>
+        <v>0.04233670057449926</v>
       </c>
       <c r="W98">
-        <v>0.1922102362592722</v>
+        <v>0.1922987905246406</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2138885393607514</v>
+        <v>0.2116835028724963</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2237291744359425</v>
+        <v>0.2252791744359425</v>
       </c>
       <c r="C99">
-        <v>-10009.01761745876</v>
+        <v>-10166.96278811892</v>
       </c>
       <c r="D99">
-        <v>2367.17638254124</v>
+        <v>2346.733211881079</v>
       </c>
       <c r="E99">
-        <v>4746.893999999998</v>
+        <v>4884.395999999999</v>
       </c>
       <c r="F99">
-        <v>13337.694</v>
+        <v>13475.196</v>
       </c>
       <c r="G99">
         <v>961.5</v>
@@ -9405,37 +9405,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M99">
-        <v>2678.2089552</v>
+        <v>2705.8193568</v>
       </c>
       <c r="N99">
-        <v>-2111.276302138775</v>
+        <v>-2138.886703738775</v>
       </c>
       <c r="O99">
-        <v>-422.2552604277551</v>
+        <v>-427.7773407477551</v>
       </c>
       <c r="P99">
-        <v>-1689.02104171102</v>
+        <v>-1711.10936299102</v>
       </c>
       <c r="Q99">
-        <v>-929.3210417110205</v>
+        <v>-951.4093629910204</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.239978254234706</v>
+        <v>1.837067381352058</v>
       </c>
       <c r="T99">
-        <v>23.27675689785016</v>
+        <v>34.91513534677523</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.04233670057449926</v>
+        <v>0.04190469342577988</v>
       </c>
       <c r="W99">
-        <v>0.1922987905246406</v>
+        <v>0.1923855375601034</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2116835028724963</v>
+        <v>0.2095234671288994</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2252791744359425</v>
+        <v>0.2268291744359425</v>
       </c>
       <c r="C100">
-        <v>-10166.96278811892</v>
+        <v>-10324.55788355367</v>
       </c>
       <c r="D100">
-        <v>2346.733211881079</v>
+        <v>2326.640116446327</v>
       </c>
       <c r="E100">
-        <v>4884.395999999999</v>
+        <v>5021.897999999999</v>
       </c>
       <c r="F100">
-        <v>13475.196</v>
+        <v>13612.698</v>
       </c>
       <c r="G100">
         <v>961.5</v>
@@ -9487,37 +9487,37 @@
         <v>566.9326530612244</v>
       </c>
       <c r="M100">
-        <v>2705.8193568</v>
+        <v>2733.4297584</v>
       </c>
       <c r="N100">
-        <v>-2138.886703738775</v>
+        <v>-2166.497105338775</v>
       </c>
       <c r="O100">
-        <v>-427.7773407477551</v>
+        <v>-433.2994210677551</v>
       </c>
       <c r="P100">
-        <v>-1711.10936299102</v>
+        <v>-1733.19768427102</v>
       </c>
       <c r="Q100">
-        <v>-951.4093629910204</v>
+        <v>-973.4976842710204</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.837067381352058</v>
+        <v>3.628334762704116</v>
       </c>
       <c r="T100">
-        <v>34.91513534677523</v>
+        <v>69.83027069355046</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.04190469342577988</v>
+        <v>0.04148141369420635</v>
       </c>
       <c r="W100">
-        <v>0.1923855375601034</v>
+        <v>0.1924705321302034</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2095234671288994</v>
+        <v>0.2074070684710316</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2268291744359425</v>
-      </c>
-      <c r="C101">
-        <v>-10324.55788355367</v>
-      </c>
-      <c r="D101">
-        <v>2326.640116446327</v>
-      </c>
-      <c r="E101">
-        <v>5021.897999999999</v>
-      </c>
-      <c r="F101">
-        <v>13612.698</v>
-      </c>
-      <c r="G101">
-        <v>961.5</v>
-      </c>
-      <c r="H101">
-        <v>5159.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1326.632653061224</v>
-      </c>
-      <c r="K101">
-        <v>759.6999999999999</v>
-      </c>
-      <c r="L101">
-        <v>566.9326530612244</v>
-      </c>
-      <c r="M101">
-        <v>2733.4297584</v>
-      </c>
-      <c r="N101">
-        <v>-2166.497105338775</v>
-      </c>
-      <c r="O101">
-        <v>-433.2994210677551</v>
-      </c>
-      <c r="P101">
-        <v>-1733.19768427102</v>
-      </c>
-      <c r="Q101">
-        <v>-973.4976842710204</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.628334762704116</v>
-      </c>
-      <c r="T101">
-        <v>69.83027069355046</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.04148141369420635</v>
-      </c>
-      <c r="W101">
-        <v>0.1924705321302034</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2074070684710316</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
